--- a/assets/TEMPLATE.xlsx
+++ b/assets/TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d15357bc9330a16b/Perso/Excel Finsight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19903" documentId="8_{70B60DCA-2A2A-4C9F-A503-36CD709D73CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1A0032C-BCB9-40BD-AC5F-D677069ACC7E}"/>
+  <xr:revisionPtr revIDLastSave="20276" documentId="8_{70B60DCA-2A2A-4C9F-A503-36CD709D73CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD778E78-ABEB-4AC2-B482-C1F7623530D9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" tabRatio="701" firstSheet="2" activeTab="8" xr2:uid="{A23352FC-3282-498A-8439-8CCDF458367F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="701" xr2:uid="{A23352FC-3282-498A-8439-8CCDF458367F}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -3996,19 +3996,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2026F</c:v>
+                  <c:v>1F</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2027F</c:v>
+                  <c:v>2F</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2028F</c:v>
+                  <c:v>3F</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2029F</c:v>
+                  <c:v>4F</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2030F</c:v>
+                  <c:v>5F</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5875,7 +5875,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0" formatCode="&quot;€&quot;#,##0_);[Red]\(&quot;€&quot;#,##0\)">
-                  <c:v>2026</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5945,7 +5945,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0" formatCode="&quot;€&quot;#,##0_);[Red]\(&quot;€&quot;#,##0\)">
-                  <c:v>2026</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6015,7 +6015,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0" formatCode="&quot;€&quot;#,##0_);[Red]\(&quot;€&quot;#,##0\)">
-                  <c:v>2026</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15565,8 +15565,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1000129" y="5505450"/>
-              <a:ext cx="4486272" cy="2324102"/>
+              <a:off x="1019179" y="5509260"/>
+              <a:ext cx="4598667" cy="2324102"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -16027,7 +16027,7 @@
               <a:picLocks noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="[1]Chart!$E$10:$L$25" spid="_x0000_s10553"/>
+                  <a14:cameraTool cellRange="[1]Chart!$E$10:$L$25" spid="_x0000_s10573"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -16085,7 +16085,7 @@
               <a:picLocks noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="[1]Chart!$E$10:$L$25" spid="_x0000_s10554"/>
+                  <a14:cameraTool cellRange="[1]Chart!$E$10:$L$25" spid="_x0000_s10574"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -16465,7 +16465,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="7">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -16491,15 +16491,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="50" style="19" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="8" width="13.28515625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="8" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="250"/>
       <c r="B1" s="118"/>
       <c r="C1" s="5"/>
@@ -16509,7 +16509,7 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -16519,7 +16519,7 @@
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="126"/>
       <c r="B3" s="15" t="s">
         <v>331</v>
@@ -16531,7 +16531,7 @@
       <c r="G3" s="23"/>
       <c r="H3" s="23"/>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="12" t="s">
         <v>1</v>
@@ -16543,7 +16543,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="251"/>
       <c r="B5" s="16" t="s">
         <v>2</v>
@@ -16552,27 +16552,27 @@
         <v>3</v>
       </c>
       <c r="D5" s="24" t="str">
-        <f>IF(1&gt;$F$128,"",IF(1=$G$128,$D$117&amp;" (LTM)",$D$117-($G$128-1)))</f>
+        <f>IF(1&gt;$F$128,"",IF(1=$G$128,VALUE($D$117)&amp;" (LTM)",VALUE($D$117)-($G$128-1)))</f>
         <v/>
       </c>
       <c r="E5" s="24" t="str">
-        <f>IF(2&gt;$F$128,"",IF(2=$G$128,$D$117&amp;" (LTM)",$D$117-($G$128-2)))</f>
+        <f>IF(2&gt;$F$128,"",IF(2=$G$128,VALUE($D$117)&amp;" (LTM)",VALUE($D$117)-($G$128-2)))</f>
         <v/>
       </c>
       <c r="F5" s="24" t="str">
-        <f>IF(3&gt;$F$128,"",IF(3=$G$128,$D$117&amp;" (LTM)",$D$117-($G$128-3)))</f>
+        <f>IF(3&gt;$F$128,"",IF(3=$G$128,VALUE($D$117)&amp;" (LTM)",VALUE($D$117)-($G$128-3)))</f>
         <v/>
       </c>
       <c r="G5" s="24" t="str">
-        <f>IF(4&gt;$F$128,"",IF(4=$G$128,$D$117&amp;" (LTM)",$D$117-($G$128-4)))</f>
+        <f>IF(4&gt;$F$128,"",IF(4=$G$128,VALUE($D$117)&amp;" (LTM)",VALUE($D$117)-($G$128-4)))</f>
         <v/>
       </c>
       <c r="H5" s="24" t="str">
-        <f>IF(5&gt;$F$128,"",IF(5=$G$128,$D$117&amp;" (LTM)",$D$117-($G$128-5)))</f>
+        <f>IF(5&gt;$F$128,"",IF(5=$G$128,VALUE($D$117)&amp;" (LTM)",VALUE($D$117)-($G$128-5)))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="14"/>
       <c r="C6" s="3"/>
@@ -16582,7 +16582,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="126" t="s">
         <v>343</v>
       </c>
@@ -16596,7 +16596,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="126"/>
       <c r="B8" s="124"/>
       <c r="C8" s="126"/>
@@ -16606,7 +16606,7 @@
       <c r="G8" s="123"/>
       <c r="H8" s="123"/>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -16620,7 +16620,7 @@
       <c r="G9" s="266"/>
       <c r="H9" s="266"/>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>6</v>
@@ -16634,7 +16634,7 @@
       <c r="G10" s="267"/>
       <c r="H10" s="267"/>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="55" t="s">
         <v>7</v>
@@ -16663,7 +16663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="55"/>
       <c r="C12" s="56"/>
@@ -16673,7 +16673,7 @@
       <c r="G12" s="57"/>
       <c r="H12" s="57"/>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="55"/>
       <c r="C13" s="56"/>
@@ -16698,7 +16698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="17" t="s">
         <v>8</v>
@@ -16712,7 +16712,7 @@
       <c r="G14" s="266"/>
       <c r="H14" s="266"/>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="17" t="s">
         <v>9</v>
@@ -16726,7 +16726,7 @@
       <c r="G15" s="266"/>
       <c r="H15" s="266"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="17" t="s">
         <v>10</v>
@@ -16740,7 +16740,7 @@
       <c r="G16" s="268"/>
       <c r="H16" s="268"/>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="55" t="s">
         <v>11</v>
@@ -16769,7 +16769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="55"/>
       <c r="C18" s="56"/>
@@ -16779,7 +16779,7 @@
       <c r="G18" s="57"/>
       <c r="H18" s="57"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="55"/>
       <c r="C19" s="56"/>
@@ -16804,7 +16804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="17" t="s">
         <v>12</v>
@@ -16818,7 +16818,7 @@
       <c r="G20" s="266"/>
       <c r="H20" s="266"/>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="17" t="s">
         <v>13</v>
@@ -16832,7 +16832,7 @@
       <c r="G21" s="268"/>
       <c r="H21" s="268"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="55" t="s">
         <v>14</v>
@@ -16861,7 +16861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="55"/>
       <c r="C23" s="56"/>
@@ -16871,7 +16871,7 @@
       <c r="G23" s="57"/>
       <c r="H23" s="57"/>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="55"/>
       <c r="C24" s="56"/>
@@ -16896,7 +16896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="17" t="s">
         <v>15</v>
@@ -16910,7 +16910,7 @@
       <c r="G25" s="266"/>
       <c r="H25" s="266"/>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3"/>
       <c r="B26" s="58" t="s">
         <v>16</v>
@@ -16939,7 +16939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="58"/>
       <c r="C27" s="56"/>
@@ -16949,7 +16949,7 @@
       <c r="G27" s="57"/>
       <c r="H27" s="57"/>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="58"/>
       <c r="C28" s="56"/>
@@ -16959,7 +16959,7 @@
       <c r="G28"/>
       <c r="H28"/>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="17" t="s">
         <v>17</v>
@@ -16973,7 +16973,7 @@
       <c r="G29" s="266"/>
       <c r="H29" s="266"/>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="55" t="s">
         <v>18</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="14"/>
       <c r="C31" s="9"/>
@@ -17012,7 +17012,7 @@
       <c r="G31" s="46"/>
       <c r="H31" s="46"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="126" t="s">
         <v>343</v>
       </c>
@@ -17026,7 +17026,7 @@
       <c r="G32" s="49"/>
       <c r="H32" s="49"/>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="126"/>
       <c r="B33" s="139"/>
       <c r="C33" s="130"/>
@@ -17036,7 +17036,7 @@
       <c r="G33" s="140"/>
       <c r="H33" s="140"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="17" t="s">
         <v>20</v>
@@ -17050,7 +17050,7 @@
       <c r="G34" s="269"/>
       <c r="H34" s="269"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="17" t="s">
         <v>21</v>
@@ -17064,7 +17064,7 @@
       <c r="G35" s="266"/>
       <c r="H35" s="266"/>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="17" t="s">
         <v>22</v>
@@ -17078,7 +17078,7 @@
       <c r="G36" s="266"/>
       <c r="H36" s="266"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="17" t="s">
         <v>23</v>
@@ -17092,7 +17092,7 @@
       <c r="G37" s="268"/>
       <c r="H37" s="268"/>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="55" t="s">
         <v>24</v>
@@ -17121,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="55"/>
       <c r="C39" s="56"/>
@@ -17131,7 +17131,7 @@
       <c r="G39" s="57"/>
       <c r="H39" s="57"/>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="55"/>
       <c r="C40" s="56"/>
@@ -17141,7 +17141,7 @@
       <c r="G40" s="57"/>
       <c r="H40" s="57"/>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="17" t="s">
         <v>25</v>
@@ -17155,7 +17155,7 @@
       <c r="G41" s="266"/>
       <c r="H41" s="266"/>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="17" t="s">
         <v>26</v>
@@ -17169,7 +17169,7 @@
       <c r="G42" s="266"/>
       <c r="H42" s="266"/>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="17" t="s">
         <v>27</v>
@@ -17183,7 +17183,7 @@
       <c r="G43" s="266"/>
       <c r="H43" s="266"/>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="3"/>
       <c r="B44" s="55" t="s">
         <v>28</v>
@@ -17212,7 +17212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="55"/>
       <c r="C45" s="56"/>
@@ -17222,7 +17222,7 @@
       <c r="G45" s="57"/>
       <c r="H45" s="57"/>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="55"/>
       <c r="C46" s="56"/>
@@ -17232,7 +17232,7 @@
       <c r="G46" s="57"/>
       <c r="H46" s="57"/>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="17" t="s">
         <v>29</v>
@@ -17246,7 +17246,7 @@
       <c r="G47" s="266"/>
       <c r="H47" s="266"/>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="17" t="s">
         <v>30</v>
@@ -17260,7 +17260,7 @@
       <c r="G48" s="266"/>
       <c r="H48" s="266"/>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="17" t="s">
         <v>31</v>
@@ -17274,7 +17274,7 @@
       <c r="G49" s="266"/>
       <c r="H49" s="266"/>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="17" t="s">
         <v>32</v>
@@ -17288,7 +17288,7 @@
       <c r="G50" s="268"/>
       <c r="H50" s="268"/>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="55" t="s">
         <v>33</v>
@@ -17317,7 +17317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="55"/>
       <c r="C52" s="56"/>
@@ -17327,7 +17327,7 @@
       <c r="G52" s="57"/>
       <c r="H52" s="57"/>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="55"/>
       <c r="C53" s="56"/>
@@ -17337,7 +17337,7 @@
       <c r="G53" s="57"/>
       <c r="H53" s="57"/>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="17" t="s">
         <v>34</v>
@@ -17351,7 +17351,7 @@
       <c r="G54" s="268"/>
       <c r="H54" s="268"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="58" t="s">
         <v>35</v>
@@ -17380,7 +17380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="58"/>
       <c r="C56" s="56"/>
@@ -17390,7 +17390,7 @@
       <c r="G56" s="57"/>
       <c r="H56" s="57"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="58"/>
       <c r="C57" s="56"/>
@@ -17400,7 +17400,7 @@
       <c r="G57" s="57"/>
       <c r="H57" s="57"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="17" t="s">
         <v>36</v>
@@ -17414,7 +17414,7 @@
       <c r="G58" s="266"/>
       <c r="H58" s="266"/>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="17" t="s">
         <v>37</v>
@@ -17422,28 +17422,13 @@
       <c r="C59" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="D59" s="276">
-        <f>D44-D55-D58</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="276">
-        <f>E44-E55-E58</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="276">
-        <f>F44-F55-F58</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="276">
-        <f>G44-G55-G58</f>
-        <v>0</v>
-      </c>
-      <c r="H59" s="276">
-        <f>H44-H55-H58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D59" s="276"/>
+      <c r="E59" s="276"/>
+      <c r="F59" s="276"/>
+      <c r="G59" s="276"/>
+      <c r="H59" s="276"/>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="58" t="s">
         <v>38</v>
@@ -17472,7 +17457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="58"/>
       <c r="C61" s="56"/>
@@ -17482,7 +17467,7 @@
       <c r="G61" s="57"/>
       <c r="H61" s="57"/>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="58"/>
       <c r="C62" s="56"/>
@@ -17492,7 +17477,7 @@
       <c r="G62" s="57"/>
       <c r="H62" s="57"/>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3"/>
       <c r="B63" s="58" t="s">
         <v>39</v>
@@ -17521,7 +17506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="58"/>
       <c r="C64" s="56"/>
@@ -17531,7 +17516,7 @@
       <c r="G64" s="57"/>
       <c r="H64" s="57"/>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="58"/>
       <c r="C65" s="56"/>
@@ -17541,7 +17526,7 @@
       <c r="G65" s="57"/>
       <c r="H65" s="57"/>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="14"/>
       <c r="C66" s="9"/>
@@ -17551,7 +17536,7 @@
       <c r="G66" s="46"/>
       <c r="H66" s="46"/>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="126"/>
       <c r="B67" s="53" t="s">
         <v>40</v>
@@ -17563,7 +17548,7 @@
       <c r="G67" s="49"/>
       <c r="H67" s="49"/>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="126"/>
       <c r="B68" s="139"/>
       <c r="C68" s="130"/>
@@ -17573,7 +17558,7 @@
       <c r="G68" s="140"/>
       <c r="H68" s="140"/>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="17" t="s">
         <v>16</v>
@@ -17602,7 +17587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="17" t="s">
         <v>10</v>
@@ -17631,7 +17616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="17" t="s">
         <v>41</v>
@@ -17645,7 +17630,7 @@
       <c r="G71" s="266"/>
       <c r="H71" s="266"/>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="17" t="s">
         <v>42</v>
@@ -17659,7 +17644,7 @@
       <c r="G72" s="266"/>
       <c r="H72" s="266"/>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="17" t="s">
         <v>43</v>
@@ -17673,7 +17658,7 @@
       <c r="G73" s="266"/>
       <c r="H73" s="266"/>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="17" t="s">
         <v>44</v>
@@ -17687,7 +17672,7 @@
       <c r="G74" s="266"/>
       <c r="H74" s="266"/>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3"/>
       <c r="B75" s="55" t="s">
         <v>45</v>
@@ -17716,7 +17701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="55"/>
       <c r="C76" s="56"/>
@@ -17726,7 +17711,7 @@
       <c r="G76" s="57"/>
       <c r="H76" s="57"/>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="55"/>
       <c r="C77" s="56"/>
@@ -17736,7 +17721,7 @@
       <c r="G77" s="57"/>
       <c r="H77" s="57"/>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="17" t="s">
         <v>46</v>
@@ -17750,7 +17735,7 @@
       <c r="G78" s="266"/>
       <c r="H78" s="266"/>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="17" t="s">
         <v>47</v>
@@ -17764,7 +17749,7 @@
       <c r="G79" s="266"/>
       <c r="H79" s="266"/>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3"/>
       <c r="B80" s="58" t="s">
         <v>48</v>
@@ -17793,7 +17778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="58"/>
       <c r="C81" s="56"/>
@@ -17803,7 +17788,7 @@
       <c r="G81" s="57"/>
       <c r="H81" s="57"/>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="58"/>
       <c r="C82" s="56"/>
@@ -17813,7 +17798,7 @@
       <c r="G82" s="57"/>
       <c r="H82" s="57"/>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="17" t="s">
         <v>49</v>
@@ -17827,7 +17812,7 @@
       <c r="G83" s="266"/>
       <c r="H83" s="266"/>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="17" t="s">
         <v>50</v>
@@ -17841,7 +17826,7 @@
       <c r="G84" s="266"/>
       <c r="H84" s="266"/>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="17" t="s">
         <v>51</v>
@@ -17855,7 +17840,7 @@
       <c r="G85" s="266"/>
       <c r="H85" s="266"/>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3"/>
       <c r="B86" s="55" t="s">
         <v>52</v>
@@ -17884,7 +17869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="55"/>
       <c r="C87" s="56"/>
@@ -17894,7 +17879,7 @@
       <c r="G87" s="57"/>
       <c r="H87" s="57"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="55"/>
       <c r="C88" s="56"/>
@@ -17904,7 +17889,7 @@
       <c r="G88" s="57"/>
       <c r="H88" s="57"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="58" t="s">
         <v>53</v>
@@ -17933,7 +17918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="17" t="s">
         <v>54</v>
@@ -17947,7 +17932,7 @@
       <c r="G90" s="266"/>
       <c r="H90" s="266"/>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3"/>
       <c r="B91" s="58" t="s">
         <v>55</v>
@@ -17976,7 +17961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="14"/>
       <c r="C92" s="9"/>
@@ -17986,7 +17971,7 @@
       <c r="G92" s="46"/>
       <c r="H92" s="46"/>
     </row>
-    <row r="93" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A93" s="126"/>
       <c r="B93" s="53" t="s">
         <v>56</v>
@@ -17998,7 +17983,7 @@
       <c r="G93" s="49"/>
       <c r="H93" s="49"/>
     </row>
-    <row r="94" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A94" s="126"/>
       <c r="B94" s="139"/>
       <c r="C94" s="130"/>
@@ -18008,7 +17993,7 @@
       <c r="G94" s="140"/>
       <c r="H94" s="140"/>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="17" t="s">
         <v>57</v>
@@ -18022,7 +18007,7 @@
       <c r="G95" s="266"/>
       <c r="H95" s="266"/>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="17" t="s">
         <v>59</v>
@@ -18036,7 +18021,7 @@
       <c r="G96" s="270"/>
       <c r="H96" s="270"/>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="17" t="s">
         <v>60</v>
@@ -18065,7 +18050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="14" t="s">
         <v>61</v>
@@ -18094,7 +18079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="17" t="s">
         <v>62</v>
@@ -18108,7 +18093,7 @@
       <c r="G99" s="266"/>
       <c r="H99" s="266"/>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="17" t="s">
         <v>64</v>
@@ -18122,7 +18107,7 @@
       <c r="G100" s="266"/>
       <c r="H100" s="266"/>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="17" t="s">
         <v>66</v>
@@ -18136,7 +18121,7 @@
       <c r="G101" s="266"/>
       <c r="H101" s="266"/>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="17" t="s">
         <v>67</v>
@@ -18160,7 +18145,7 @@
         <v>0.10630000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="17" t="s">
         <v>68</v>
@@ -18174,7 +18159,7 @@
       <c r="G103" s="266"/>
       <c r="H103" s="266"/>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="17" t="s">
         <v>69</v>
@@ -18188,7 +18173,7 @@
       <c r="G104" s="266"/>
       <c r="H104" s="266"/>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="17" t="s">
         <v>70</v>
@@ -18212,7 +18197,7 @@
         <v>3.6299999999999999E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="17" t="s">
         <v>71</v>
@@ -18226,7 +18211,7 @@
       <c r="G106" s="266"/>
       <c r="H106" s="266"/>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="17" t="s">
         <v>72</v>
@@ -18240,7 +18225,7 @@
       <c r="G107" s="266"/>
       <c r="H107" s="266"/>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="14" t="s">
         <v>73</v>
@@ -18269,7 +18254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="17" t="s">
         <v>74</v>
@@ -18283,7 +18268,7 @@
       <c r="G109" s="266"/>
       <c r="H109" s="266"/>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="17" t="s">
         <v>75</v>
@@ -18297,7 +18282,7 @@
       <c r="G110" s="266"/>
       <c r="H110" s="266"/>
     </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="14"/>
       <c r="C111" s="9"/>
@@ -18307,7 +18292,7 @@
       <c r="G111" s="46"/>
       <c r="H111" s="46"/>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A112" s="126"/>
       <c r="B112" s="53" t="s">
         <v>77</v>
@@ -18319,7 +18304,7 @@
       <c r="G112" s="49"/>
       <c r="H112" s="49"/>
     </row>
-    <row r="113" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A113" s="126"/>
       <c r="B113" s="139"/>
       <c r="C113" s="130"/>
@@ -18329,7 +18314,7 @@
       <c r="G113" s="140"/>
       <c r="H113" s="140"/>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="14" t="s">
         <v>78</v>
@@ -18343,7 +18328,7 @@
       <c r="G114" s="46"/>
       <c r="H114" s="46"/>
     </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="14" t="s">
         <v>80</v>
@@ -18357,7 +18342,7 @@
       <c r="G115" s="46"/>
       <c r="H115" s="46"/>
     </row>
-    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="14" t="s">
         <v>81</v>
@@ -18371,7 +18356,7 @@
       <c r="G116" s="46"/>
       <c r="H116" s="46"/>
     </row>
-    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="86" t="s">
         <v>342</v>
@@ -18379,15 +18364,13 @@
       <c r="C117" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="D117" s="95">
-        <v>2025</v>
-      </c>
+      <c r="D117" s="95"/>
       <c r="E117" s="46"/>
       <c r="F117" s="46"/>
       <c r="G117" s="46"/>
       <c r="H117" s="46"/>
     </row>
-    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="14" t="s">
         <v>83</v>
@@ -18401,7 +18384,7 @@
       <c r="G118" s="46"/>
       <c r="H118" s="46"/>
     </row>
-    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="14" t="s">
         <v>84</v>
@@ -18415,7 +18398,7 @@
       <c r="G119" s="46"/>
       <c r="H119" s="46"/>
     </row>
-    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="14" t="s">
         <v>85</v>
@@ -18429,7 +18412,7 @@
       <c r="G120" s="273"/>
       <c r="H120" s="273"/>
     </row>
-    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="14"/>
       <c r="C121" s="9"/>
@@ -18439,7 +18422,7 @@
       <c r="G121" s="46"/>
       <c r="H121" s="46"/>
     </row>
-    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="54" t="s">
         <v>332</v>
@@ -18451,7 +18434,7 @@
       <c r="G122" s="22"/>
       <c r="H122" s="22"/>
     </row>
-    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="14"/>
       <c r="C123" s="3"/>
@@ -18461,7 +18444,7 @@
       <c r="G123" s="22"/>
       <c r="H123" s="22"/>
     </row>
-    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="250"/>
       <c r="B124" s="33" t="s">
         <v>339</v>
@@ -18473,7 +18456,7 @@
       <c r="G124" s="25"/>
       <c r="H124" s="25"/>
     </row>
-    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="250"/>
       <c r="B125" s="33" t="s">
         <v>86</v>
@@ -18485,7 +18468,7 @@
       <c r="G125" s="25"/>
       <c r="H125" s="25"/>
     </row>
-    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="250"/>
       <c r="B126" s="33" t="s">
         <v>340</v>
@@ -18497,24 +18480,24 @@
       <c r="G126" s="25"/>
       <c r="H126" s="25"/>
     </row>
-    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="51"/>
     </row>
-    <row r="128" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="417"/>
       <c r="B128" s="418"/>
       <c r="C128" s="417"/>
       <c r="D128" s="419">
-        <f>COUNTIF(D9:G9,"&lt;&gt;")</f>
+        <f>IF(COUNTA(D9,D10,D14,D15,D16,D20,D21,D25)=8,1,0)+IF(COUNTA(E9,E10,E14,E15,E16,E20,E21,E25)=8,1,0)+IF(COUNTA(F9,F10,F14,F15,F16,F20,F21,F25)=8,1,0)+IF(COUNTA(G9,G10,G14,G15,G16,G20,G21,G25)=8,1,0)</f>
         <v>0</v>
       </c>
       <c r="E128" s="419"/>
       <c r="F128" s="419">
-        <f>D128+IF(H9&lt;&gt;"",1,0)</f>
+        <f>IF(COUNTA(D9,D10,D14,D15,D16,D20,D21,D25)=8,1,0)+IF(COUNTA(E9,E10,E14,E15,E16,E20,E21,E25)=8,1,0)+IF(COUNTA(F9,F10,F14,F15,F16,F20,F21,F25)=8,1,0)+IF(COUNTA(G9,G10,G14,G15,G16,G20,G21,G25)=8,1,0)+IF(COUNTA(H9,H10,H14,H15,H16,H20,H21,H25)=8,1,0)</f>
         <v>0</v>
       </c>
       <c r="G128" s="419">
-        <f>IF(H9&lt;&gt;"",D128+1,D128)</f>
+        <f>IF(COUNTA(H9,H10,H14,H15,H16,H20,H21,H25)=8,$F$128,IF(COUNTA(G9,G10,G14,G15,G16,G20,G21,G25)=8,$F$128,IF(COUNTA(F9,F10,F14,F15,F16,F20,F21,F25)=8,$F$128,IF(COUNTA(E9,E10,E14,E15,E16,E20,E21,E25)=8,$F$128,IF(COUNTA(D9,D10,D14,D15,D16,D20,D21,D25)=8,$F$128,0)))))</f>
         <v>0</v>
       </c>
       <c r="H128" s="419"/>
@@ -18522,73 +18505,73 @@
       <c r="J128" s="417"/>
       <c r="K128" s="417"/>
     </row>
-    <row r="129" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="51"/>
     </row>
-    <row r="130" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="51"/>
     </row>
-    <row r="131" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="51"/>
     </row>
-    <row r="132" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="51"/>
     </row>
-    <row r="133" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="51"/>
     </row>
-    <row r="134" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="51"/>
     </row>
-    <row r="135" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="51"/>
     </row>
-    <row r="136" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="51"/>
     </row>
-    <row r="137" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="51"/>
     </row>
-    <row r="138" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="51"/>
     </row>
-    <row r="139" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="51"/>
     </row>
-    <row r="140" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="51"/>
     </row>
-    <row r="141" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="51"/>
     </row>
-    <row r="142" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="51"/>
     </row>
-    <row r="143" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="51"/>
     </row>
-    <row r="144" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="51"/>
     </row>
-    <row r="145" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="51"/>
     </row>
-    <row r="146" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="51"/>
     </row>
-    <row r="147" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="51"/>
     </row>
-    <row r="148" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="51"/>
     </row>
-    <row r="149" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="51"/>
     </row>
-    <row r="150" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="51"/>
     </row>
-    <row r="151" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="51"/>
     </row>
   </sheetData>
@@ -18631,22 +18614,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633274F7-3F6A-4E64-A480-2B4994687C63}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="198" t="s">
         <v>417</v>
       </c>
       <c r="B1" s="198"/>
       <c r="C1" s="198"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="199" t="s">
         <v>419</v>
       </c>
@@ -18657,7 +18640,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="286">
         <v>1</v>
       </c>
@@ -18668,7 +18651,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="286">
         <v>2</v>
       </c>
@@ -18679,7 +18662,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="286">
         <v>3</v>
       </c>
@@ -18690,7 +18673,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="286">
         <v>4</v>
       </c>
@@ -18701,7 +18684,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="286">
         <v>5</v>
       </c>
@@ -18712,7 +18695,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="286">
         <v>6</v>
       </c>
@@ -18723,7 +18706,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="286">
         <v>7</v>
       </c>
@@ -18734,7 +18717,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="286">
         <v>8</v>
       </c>
@@ -18745,7 +18728,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="286">
         <v>9</v>
       </c>
@@ -18756,7 +18739,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="286">
         <v>10</v>
       </c>
@@ -18767,7 +18750,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="286">
         <v>11</v>
       </c>
@@ -18778,7 +18761,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="286">
         <v>12</v>
       </c>
@@ -18789,7 +18772,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="286">
         <v>13</v>
       </c>
@@ -18800,7 +18783,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="200" t="s">
         <v>433</v>
       </c>
@@ -18816,16 +18799,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="198" t="s">
         <v>444</v>
       </c>
@@ -18842,7 +18825,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>449</v>
       </c>
@@ -18859,7 +18842,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>449</v>
       </c>
@@ -18876,7 +18859,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>449</v>
       </c>
@@ -18893,7 +18876,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>449</v>
       </c>
@@ -18910,7 +18893,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>449</v>
       </c>
@@ -18927,7 +18910,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>449</v>
       </c>
@@ -18944,7 +18927,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>449</v>
       </c>
@@ -18961,7 +18944,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>449</v>
       </c>
@@ -18978,7 +18961,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>449</v>
       </c>
@@ -18995,7 +18978,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>449</v>
       </c>
@@ -19012,7 +18995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>455</v>
       </c>
@@ -19029,7 +19012,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>455</v>
       </c>
@@ -19046,7 +19029,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>455</v>
       </c>
@@ -19063,7 +19046,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>455</v>
       </c>
@@ -19080,7 +19063,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>455</v>
       </c>
@@ -19097,7 +19080,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>455</v>
       </c>
@@ -19114,7 +19097,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>455</v>
       </c>
@@ -19131,7 +19114,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>455</v>
       </c>
@@ -19148,7 +19131,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>455</v>
       </c>
@@ -19165,7 +19148,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>455</v>
       </c>
@@ -19182,7 +19165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>456</v>
       </c>
@@ -19199,7 +19182,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>456</v>
       </c>
@@ -19216,7 +19199,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>456</v>
       </c>
@@ -19233,7 +19216,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>456</v>
       </c>
@@ -19250,7 +19233,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>456</v>
       </c>
@@ -19267,7 +19250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>456</v>
       </c>
@@ -19284,7 +19267,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>456</v>
       </c>
@@ -19301,7 +19284,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>456</v>
       </c>
@@ -19318,7 +19301,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>456</v>
       </c>
@@ -19335,7 +19318,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>456</v>
       </c>
@@ -19352,7 +19335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>457</v>
       </c>
@@ -19369,7 +19352,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>457</v>
       </c>
@@ -19386,7 +19369,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>457</v>
       </c>
@@ -19403,7 +19386,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>457</v>
       </c>
@@ -19420,7 +19403,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>457</v>
       </c>
@@ -19437,7 +19420,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>457</v>
       </c>
@@ -19454,7 +19437,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>457</v>
       </c>
@@ -19471,7 +19454,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>457</v>
       </c>
@@ -19488,7 +19471,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>457</v>
       </c>
@@ -19505,7 +19488,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>457</v>
       </c>
@@ -19522,7 +19505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>458</v>
       </c>
@@ -19539,7 +19522,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>458</v>
       </c>
@@ -19556,7 +19539,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>458</v>
       </c>
@@ -19573,7 +19556,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>458</v>
       </c>
@@ -19590,7 +19573,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>458</v>
       </c>
@@ -19607,7 +19590,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>458</v>
       </c>
@@ -19624,7 +19607,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>458</v>
       </c>
@@ -19641,7 +19624,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>458</v>
       </c>
@@ -19658,7 +19641,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>458</v>
       </c>
@@ -19675,7 +19658,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>458</v>
       </c>
@@ -19692,7 +19675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>459</v>
       </c>
@@ -19709,7 +19692,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>459</v>
       </c>
@@ -19726,7 +19709,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>459</v>
       </c>
@@ -19743,7 +19726,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>459</v>
       </c>
@@ -19760,7 +19743,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>459</v>
       </c>
@@ -19777,7 +19760,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>459</v>
       </c>
@@ -19794,7 +19777,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>459</v>
       </c>
@@ -19811,7 +19794,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>459</v>
       </c>
@@ -19828,7 +19811,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>459</v>
       </c>
@@ -19845,7 +19828,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>459</v>
       </c>
@@ -19874,15 +19857,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="229" customWidth="1"/>
-    <col min="2" max="2" width="49.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="8" width="13.28515625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="8" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="225"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -19896,7 +19879,7 @@
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="226"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -19906,7 +19889,7 @@
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="227"/>
       <c r="B3" s="15" t="s">
         <v>87</v>
@@ -19918,7 +19901,7 @@
       <c r="G3" s="23"/>
       <c r="H3" s="23"/>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="226"/>
       <c r="B4" s="13"/>
       <c r="C4" s="3"/>
@@ -19928,7 +19911,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="228" t="s">
         <v>343</v>
       </c>
@@ -19957,7 +19940,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="226"/>
       <c r="B6" s="14"/>
       <c r="C6" s="3"/>
@@ -19967,7 +19950,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="227" t="s">
         <v>343</v>
       </c>
@@ -19981,7 +19964,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="227"/>
       <c r="B8" s="124"/>
       <c r="C8" s="126"/>
@@ -19991,7 +19974,7 @@
       <c r="G8" s="123"/>
       <c r="H8" s="123"/>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="226"/>
       <c r="B9" s="27" t="s">
         <v>88</v>
@@ -20018,7 +20001,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="226"/>
       <c r="B10" s="27" t="s">
         <v>89</v>
@@ -20045,7 +20028,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="226"/>
       <c r="B11" s="27" t="s">
         <v>90</v>
@@ -20072,7 +20055,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="226"/>
       <c r="B12" s="27" t="s">
         <v>91</v>
@@ -20099,7 +20082,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="226"/>
       <c r="B13" s="27" t="s">
         <v>92</v>
@@ -20126,7 +20109,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="226"/>
       <c r="B14" s="27" t="s">
         <v>93</v>
@@ -20153,7 +20136,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="226"/>
       <c r="B15" s="27" t="s">
         <v>94</v>
@@ -20180,7 +20163,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="226"/>
       <c r="B16" s="28"/>
       <c r="C16" s="9"/>
@@ -20190,7 +20173,7 @@
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="227" t="s">
         <v>343</v>
       </c>
@@ -20204,7 +20187,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="227"/>
       <c r="B18" s="139"/>
       <c r="C18" s="130"/>
@@ -20214,7 +20197,7 @@
       <c r="G18" s="123"/>
       <c r="H18" s="123"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="226"/>
       <c r="B19" s="27" t="s">
         <v>95</v>
@@ -20241,7 +20224,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="226"/>
       <c r="B20" s="27" t="s">
         <v>96</v>
@@ -20268,7 +20251,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="226"/>
       <c r="B21" s="27" t="s">
         <v>97</v>
@@ -20295,7 +20278,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="226"/>
       <c r="B22" s="27" t="s">
         <v>98</v>
@@ -20322,7 +20305,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="226"/>
       <c r="B23" s="27" t="s">
         <v>99</v>
@@ -20349,7 +20332,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="226"/>
       <c r="B24" s="27" t="s">
         <v>100</v>
@@ -20376,7 +20359,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="226"/>
       <c r="B25" s="27" t="s">
         <v>101</v>
@@ -20403,7 +20386,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="226"/>
       <c r="B26" s="28"/>
       <c r="C26" s="9"/>
@@ -20413,7 +20396,7 @@
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="227" t="s">
         <v>343</v>
       </c>
@@ -20427,7 +20410,7 @@
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="227"/>
       <c r="B28" s="139"/>
       <c r="C28" s="130"/>
@@ -20437,7 +20420,7 @@
       <c r="G28" s="123"/>
       <c r="H28" s="123"/>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="226"/>
       <c r="B29" s="27" t="s">
         <v>102</v>
@@ -20464,7 +20447,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="226"/>
       <c r="B30" s="27" t="s">
         <v>103</v>
@@ -20491,7 +20474,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="226"/>
       <c r="B31" s="27" t="s">
         <v>104</v>
@@ -20518,7 +20501,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="226"/>
       <c r="B32" s="27" t="s">
         <v>105</v>
@@ -20545,7 +20528,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="226"/>
       <c r="B33" s="27" t="s">
         <v>106</v>
@@ -20572,7 +20555,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="226"/>
       <c r="B34" s="27" t="s">
         <v>107</v>
@@ -20599,7 +20582,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="226"/>
       <c r="B35" s="27" t="s">
         <v>108</v>
@@ -20626,7 +20609,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="226"/>
       <c r="B36" s="27" t="s">
         <v>109</v>
@@ -20653,7 +20636,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="226"/>
       <c r="B37" s="28"/>
       <c r="C37" s="9"/>
@@ -20663,7 +20646,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="227" t="s">
         <v>343</v>
       </c>
@@ -20677,7 +20660,7 @@
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="227"/>
       <c r="B39" s="139"/>
       <c r="C39" s="130"/>
@@ -20687,7 +20670,7 @@
       <c r="G39" s="123"/>
       <c r="H39" s="123"/>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="226"/>
       <c r="B40" s="27" t="s">
         <v>110</v>
@@ -20714,7 +20697,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="226"/>
       <c r="B41" s="27" t="s">
         <v>111</v>
@@ -20741,7 +20724,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="226"/>
       <c r="B42" s="27" t="s">
         <v>112</v>
@@ -20768,7 +20751,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="226"/>
       <c r="B43" s="27" t="s">
         <v>113</v>
@@ -20795,7 +20778,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="226"/>
       <c r="B44" s="27" t="s">
         <v>114</v>
@@ -20822,7 +20805,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="226"/>
       <c r="B45" s="27" t="s">
         <v>115</v>
@@ -20849,7 +20832,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="226"/>
       <c r="B46" s="27" t="s">
         <v>116</v>
@@ -20876,7 +20859,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="226"/>
       <c r="B47" s="27" t="s">
         <v>117</v>
@@ -20903,7 +20886,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="226"/>
       <c r="B48" s="28"/>
       <c r="C48" s="9"/>
@@ -20913,7 +20896,7 @@
       <c r="G48" s="31"/>
       <c r="H48" s="31"/>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="227" t="s">
         <v>343</v>
       </c>
@@ -20927,7 +20910,7 @@
       <c r="G49" s="23"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="227"/>
       <c r="B50" s="139"/>
       <c r="C50" s="130"/>
@@ -20937,7 +20920,7 @@
       <c r="G50" s="123"/>
       <c r="H50" s="123"/>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="226"/>
       <c r="B51" s="27" t="s">
         <v>118</v>
@@ -20963,7 +20946,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="226"/>
       <c r="B52" s="27" t="s">
         <v>119</v>
@@ -20989,7 +20972,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="226"/>
       <c r="B53" s="27" t="s">
         <v>120</v>
@@ -21015,7 +20998,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="226"/>
       <c r="B54" s="27" t="s">
         <v>121</v>
@@ -21041,7 +21024,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="226"/>
       <c r="B55" s="27" t="s">
         <v>122</v>
@@ -21067,7 +21050,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="226"/>
       <c r="B56" s="27" t="s">
         <v>123</v>
@@ -21093,7 +21076,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="226"/>
       <c r="B57" s="28"/>
       <c r="C57" s="9"/>
@@ -21103,7 +21086,7 @@
       <c r="G57" s="31"/>
       <c r="H57" s="31"/>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A58" s="227" t="s">
         <v>343</v>
       </c>
@@ -21117,7 +21100,7 @@
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="227"/>
       <c r="B59" s="139"/>
       <c r="C59" s="130"/>
@@ -21127,7 +21110,7 @@
       <c r="G59" s="123"/>
       <c r="H59" s="123"/>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="226"/>
       <c r="B60" s="27" t="s">
         <v>124</v>
@@ -21154,7 +21137,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="226"/>
       <c r="B61" s="68" t="s">
         <v>125</v>
@@ -21181,7 +21164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="226"/>
       <c r="B62" s="27" t="s">
         <v>126</v>
@@ -21208,7 +21191,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="226"/>
       <c r="B63" s="27" t="s">
         <v>127</v>
@@ -21235,7 +21218,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="226"/>
       <c r="B64" s="27" t="s">
         <v>128</v>
@@ -21262,7 +21245,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="226"/>
       <c r="B65" s="27" t="s">
         <v>129</v>
@@ -21289,7 +21272,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="226"/>
       <c r="B66" s="27" t="s">
         <v>130</v>
@@ -21316,7 +21299,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="226"/>
       <c r="B67" s="14"/>
       <c r="C67" s="9"/>
@@ -21326,7 +21309,7 @@
       <c r="G67" s="22"/>
       <c r="H67" s="22"/>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="225"/>
       <c r="B68" s="33" t="s">
         <v>339</v>
@@ -21338,7 +21321,7 @@
       <c r="G68" s="96"/>
       <c r="H68" s="96"/>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="225"/>
       <c r="B69" s="33" t="s">
         <v>86</v>
@@ -21350,7 +21333,7 @@
       <c r="G69" s="96"/>
       <c r="H69" s="96"/>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="225"/>
       <c r="B70" s="33" t="s">
         <v>340</v>
@@ -21362,13 +21345,13 @@
       <c r="G70" s="96"/>
       <c r="H70" s="96"/>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="119" t="s">
         <v>353</v>
       </c>
@@ -21379,7 +21362,7 @@
       <c r="G73" s="122"/>
       <c r="H73" s="122"/>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="103" t="s">
         <v>354</v>
       </c>
@@ -21405,7 +21388,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="51" t="s">
         <v>316</v>
       </c>
@@ -21430,7 +21413,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="51" t="s">
         <v>409</v>
       </c>
@@ -21455,7 +21438,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="51" t="s">
         <v>410</v>
       </c>
@@ -21480,7 +21463,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="51" t="s">
         <v>411</v>
       </c>
@@ -21505,10 +21488,10 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="51"/>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="51" t="s">
         <v>95</v>
       </c>
@@ -21533,7 +21516,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="51" t="s">
         <v>96</v>
       </c>
@@ -21558,7 +21541,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="51" t="s">
         <v>98</v>
       </c>
@@ -21583,10 +21566,10 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="51"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84"/>
       <c r="D84" s="286" t="e">
         <f>IF(INPUT!D9="",NA(),D5)</f>
@@ -21609,7 +21592,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="51" t="s">
         <v>412</v>
       </c>
@@ -21634,7 +21617,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="51" t="s">
         <v>413</v>
       </c>
@@ -21659,7 +21642,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="51" t="s">
         <v>414</v>
       </c>
@@ -21684,7 +21667,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="51" t="s">
         <v>415</v>
       </c>
@@ -21709,10 +21692,10 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="51"/>
     </row>
-    <row r="90" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90"/>
       <c r="D90"/>
       <c r="E90"/>
@@ -21720,7 +21703,7 @@
       <c r="G90"/>
       <c r="H90"/>
     </row>
-    <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="51" t="s">
         <v>439</v>
       </c>
@@ -21745,7 +21728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="51" t="s">
         <v>440</v>
       </c>
@@ -21770,7 +21753,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="51" t="s">
         <v>441</v>
       </c>
@@ -21795,7 +21778,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="51" t="s">
         <v>442</v>
       </c>
@@ -21820,7 +21803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="51"/>
       <c r="D95"/>
       <c r="G95" s="287" t="e">
@@ -21832,11 +21815,11 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
       <c r="D96"/>
     </row>
-    <row r="97" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51" t="s">
         <v>443</v>
       </c>
@@ -21861,10 +21844,10 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
     </row>
-    <row r="99" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
       <c r="G99" s="287" t="e">
         <f>G78/1000</f>
@@ -21875,76 +21858,76 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
     </row>
-    <row r="101" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
     </row>
-    <row r="102" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
     </row>
-    <row r="103" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
     </row>
-    <row r="104" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
     </row>
-    <row r="105" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
     </row>
-    <row r="106" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
     </row>
-    <row r="107" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
     </row>
-    <row r="108" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
     </row>
-    <row r="109" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
     </row>
-    <row r="110" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
     </row>
-    <row r="111" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
     </row>
-    <row r="112" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
     </row>
-    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
     </row>
-    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
     </row>
-    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
     </row>
-    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
     </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
     </row>
-    <row r="121" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="51"/>
     </row>
-    <row r="122" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="51"/>
     </row>
-    <row r="123" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="51"/>
     </row>
   </sheetData>
@@ -22121,18 +22104,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="53" style="19" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="21" customWidth="1"/>
-    <col min="5" max="8" width="13.28515625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" style="21" customWidth="1"/>
+    <col min="5" max="8" width="13.33203125" style="21" customWidth="1"/>
     <col min="9" max="9" width="1" style="21" customWidth="1"/>
-    <col min="10" max="14" width="11.5703125" style="21"/>
+    <col min="10" max="14" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="6"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -22152,7 +22135,7 @@
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -22163,7 +22146,7 @@
       <c r="H2" s="22"/>
       <c r="I2" s="22"/>
     </row>
-    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="7"/>
       <c r="B3" s="15" t="s">
         <v>131</v>
@@ -22181,7 +22164,7 @@
       <c r="M3" s="47"/>
       <c r="N3" s="47"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="13"/>
       <c r="C4" s="3"/>
@@ -22192,7 +22175,7 @@
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="138" t="s">
         <v>132</v>
@@ -22225,7 +22208,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="14"/>
       <c r="C6" s="3"/>
@@ -22236,7 +22219,7 @@
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
         <v>343</v>
       </c>
@@ -22256,7 +22239,7 @@
       <c r="M7" s="47"/>
       <c r="N7" s="47"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="127" t="s">
         <v>133</v>
@@ -22284,7 +22267,7 @@
       </c>
       <c r="I8" s="30"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="127" t="s">
         <v>28</v>
@@ -22312,7 +22295,7 @@
       </c>
       <c r="I9" s="30"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="127" t="s">
         <v>37</v>
@@ -22340,7 +22323,7 @@
       </c>
       <c r="I10" s="30"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="127" t="s">
         <v>134</v>
@@ -22368,7 +22351,7 @@
       </c>
       <c r="I11" s="30"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="127" t="s">
         <v>135</v>
@@ -22396,7 +22379,7 @@
       </c>
       <c r="I12" s="30"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="127" t="s">
         <v>35</v>
@@ -22424,7 +22407,7 @@
       </c>
       <c r="I13" s="30"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="127" t="s">
         <v>5</v>
@@ -22452,7 +22435,7 @@
       </c>
       <c r="I14" s="30"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="112"/>
       <c r="C15" s="128"/>
@@ -22463,7 +22446,7 @@
       <c r="H15" s="129"/>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="7" t="s">
         <v>343</v>
       </c>
@@ -22483,7 +22466,7 @@
       <c r="M16" s="47"/>
       <c r="N16" s="47"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="127" t="s">
         <v>137</v>
@@ -22511,7 +22494,7 @@
       </c>
       <c r="I17" s="30"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="127" t="s">
         <v>138</v>
@@ -22539,7 +22522,7 @@
       </c>
       <c r="I18" s="30"/>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="127" t="s">
         <v>139</v>
@@ -22567,7 +22550,7 @@
       </c>
       <c r="I19" s="30"/>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="127" t="s">
         <v>140</v>
@@ -22595,7 +22578,7 @@
       </c>
       <c r="I20" s="30"/>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="127" t="s">
         <v>141</v>
@@ -22623,7 +22606,7 @@
       </c>
       <c r="I21" s="30"/>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="112"/>
       <c r="C22" s="128"/>
@@ -22634,7 +22617,7 @@
       <c r="H22" s="129"/>
       <c r="I22" s="22"/>
     </row>
-    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7" t="s">
         <v>343</v>
       </c>
@@ -22654,7 +22637,7 @@
       <c r="M23" s="47"/>
       <c r="N23" s="47"/>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="127" t="s">
         <v>143</v>
@@ -22682,7 +22665,7 @@
       </c>
       <c r="I24" s="30"/>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="127" t="s">
         <v>144</v>
@@ -22710,7 +22693,7 @@
       </c>
       <c r="I25" s="30"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="127" t="s">
         <v>145</v>
@@ -22738,7 +22721,7 @@
       </c>
       <c r="I26" s="30"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="127" t="s">
         <v>146</v>
@@ -22766,7 +22749,7 @@
       </c>
       <c r="I27" s="30"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="127" t="s">
         <v>147</v>
@@ -22794,7 +22777,7 @@
       </c>
       <c r="I28" s="30"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="112"/>
       <c r="C29" s="128"/>
@@ -22805,7 +22788,7 @@
       <c r="H29" s="129"/>
       <c r="I29" s="22"/>
     </row>
-    <row r="30" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="126" t="s">
         <v>343</v>
       </c>
@@ -22840,7 +22823,7 @@
       <c r="M30" s="108"/>
       <c r="N30" s="108"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="112"/>
       <c r="C31" s="128"/>
@@ -22851,7 +22834,7 @@
       <c r="H31" s="129"/>
       <c r="I31" s="22"/>
     </row>
-    <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="7" t="s">
         <v>343</v>
       </c>
@@ -22871,7 +22854,7 @@
       <c r="M32" s="47"/>
       <c r="N32" s="47"/>
     </row>
-    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="112" t="s">
         <v>150</v>
@@ -22899,7 +22882,7 @@
       </c>
       <c r="I33" s="22"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="112"/>
       <c r="C34" s="128"/>
@@ -22910,7 +22893,7 @@
       <c r="H34" s="129"/>
       <c r="I34" s="22"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="112" t="s">
         <v>151</v>
@@ -22925,7 +22908,7 @@
       <c r="H35" s="129"/>
       <c r="I35" s="61"/>
     </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="112" t="s">
         <v>153</v>
@@ -22940,7 +22923,7 @@
       <c r="H36" s="129"/>
       <c r="I36" s="61"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="112" t="s">
         <v>155</v>
@@ -22955,7 +22938,7 @@
       <c r="H37" s="129"/>
       <c r="I37" s="61"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="112"/>
       <c r="C38" s="128"/>
@@ -22966,7 +22949,7 @@
       <c r="H38" s="129"/>
       <c r="I38" s="22"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="132" t="s">
         <v>157</v>
@@ -22979,7 +22962,7 @@
       <c r="H39" s="129"/>
       <c r="I39" s="22"/>
     </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="132" t="s">
         <v>158</v>
@@ -22992,7 +22975,7 @@
       <c r="H40" s="129"/>
       <c r="I40" s="22"/>
     </row>
-    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="112"/>
       <c r="C41" s="133"/>
@@ -23003,7 +22986,7 @@
       <c r="H41" s="129"/>
       <c r="I41" s="22"/>
     </row>
-    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="96"/>
       <c r="C42" s="96"/>
@@ -23019,7 +23002,7 @@
       <c r="M42" s="96"/>
       <c r="N42" s="96"/>
     </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="96"/>
       <c r="C43" s="96"/>
@@ -23035,7 +23018,7 @@
       <c r="M43" s="96"/>
       <c r="N43" s="96"/>
     </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="96"/>
       <c r="C44" s="96"/>
@@ -23051,232 +23034,232 @@
       <c r="M44" s="96"/>
       <c r="N44" s="96"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="51"/>
     </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="51"/>
     </row>
-    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="51"/>
     </row>
-    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="51"/>
     </row>
-    <row r="49" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="51"/>
     </row>
-    <row r="50" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="51"/>
     </row>
-    <row r="51" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="51"/>
     </row>
-    <row r="52" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="51"/>
     </row>
-    <row r="53" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="51"/>
     </row>
-    <row r="54" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="51"/>
     </row>
-    <row r="55" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="51"/>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="51"/>
     </row>
-    <row r="57" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="51"/>
     </row>
-    <row r="58" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="51"/>
     </row>
-    <row r="59" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="51"/>
     </row>
-    <row r="60" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="51"/>
     </row>
-    <row r="61" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="51"/>
     </row>
-    <row r="62" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="51"/>
     </row>
-    <row r="63" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="51"/>
     </row>
-    <row r="64" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="51"/>
     </row>
-    <row r="65" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="51"/>
     </row>
-    <row r="66" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="51"/>
     </row>
-    <row r="67" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="51"/>
     </row>
-    <row r="68" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="51"/>
     </row>
-    <row r="69" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="51"/>
     </row>
-    <row r="70" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="51"/>
     </row>
-    <row r="71" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
     </row>
-    <row r="72" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
     </row>
-    <row r="73" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="51"/>
     </row>
-    <row r="74" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="51"/>
     </row>
-    <row r="75" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="51"/>
     </row>
-    <row r="76" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="51"/>
     </row>
-    <row r="77" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="51"/>
     </row>
-    <row r="78" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="51"/>
     </row>
-    <row r="79" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="51"/>
     </row>
-    <row r="80" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="51"/>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="51"/>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="51"/>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="51"/>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="51"/>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="51"/>
     </row>
-    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="51"/>
     </row>
-    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="51"/>
     </row>
-    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="51"/>
     </row>
-    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="51"/>
     </row>
-    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="51"/>
     </row>
-    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="51"/>
     </row>
-    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="51"/>
     </row>
-    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="51"/>
     </row>
-    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="51"/>
     </row>
-    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="51"/>
     </row>
-    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51"/>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
     </row>
-    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
     </row>
-    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
     </row>
-    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
     </row>
-    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
     </row>
-    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
     </row>
-    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
     </row>
-    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
     </row>
-    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
     </row>
-    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
     </row>
-    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
     </row>
-    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
     </row>
-    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
     </row>
-    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
     </row>
-    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
     </row>
-    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
     </row>
-    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
     </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
     </row>
   </sheetData>
@@ -23453,18 +23436,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="53" style="19" customWidth="1"/>
     <col min="3" max="3" width="1" style="19" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="11.5703125" style="21"/>
+    <col min="4" max="5" width="13.33203125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="6"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -23483,7 +23466,7 @@
       <c r="L1" s="20"/>
       <c r="M1" s="20"/>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -23491,7 +23474,7 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
     </row>
-    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="7"/>
       <c r="B3" s="15" t="s">
         <v>159</v>
@@ -23508,7 +23491,7 @@
       <c r="L3" s="47"/>
       <c r="M3" s="47"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -23516,7 +23499,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="16" t="s">
         <v>160</v>
@@ -23543,7 +23526,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -23552,7 +23535,7 @@
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
     </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
         <v>343</v>
       </c>
@@ -23571,7 +23554,7 @@
       <c r="L7" s="47"/>
       <c r="M7" s="47"/>
     </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="126"/>
       <c r="B8" s="124"/>
       <c r="C8" s="124"/>
@@ -23586,7 +23569,7 @@
       <c r="L8" s="108"/>
       <c r="M8" s="108"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>164</v>
@@ -23603,7 +23586,7 @@
       </c>
       <c r="G9" s="61"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>165</v>
@@ -23620,7 +23603,7 @@
       </c>
       <c r="G10" s="61"/>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="17" t="s">
         <v>7</v>
@@ -23637,7 +23620,7 @@
       </c>
       <c r="G11" s="61"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="17" t="s">
         <v>24</v>
@@ -23654,7 +23637,7 @@
       </c>
       <c r="G12" s="61"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="17" t="s">
         <v>25</v>
@@ -23671,7 +23654,7 @@
       </c>
       <c r="G13" s="61"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="17" t="s">
         <v>28</v>
@@ -23688,7 +23671,7 @@
       </c>
       <c r="G14" s="61"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="17" t="s">
         <v>33</v>
@@ -23705,7 +23688,7 @@
       </c>
       <c r="G15" s="61"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="17" t="s">
         <v>34</v>
@@ -23722,7 +23705,7 @@
       </c>
       <c r="G16" s="61"/>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="17" t="s">
         <v>16</v>
@@ -23739,7 +23722,7 @@
       </c>
       <c r="G17" s="61"/>
     </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="17" t="s">
         <v>166</v>
@@ -23756,7 +23739,7 @@
       </c>
       <c r="G18" s="61"/>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="17" t="s">
         <v>10</v>
@@ -23773,7 +23756,7 @@
       </c>
       <c r="G19" s="61"/>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="17" t="s">
         <v>167</v>
@@ -23790,7 +23773,7 @@
       </c>
       <c r="G20" s="61"/>
     </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -23798,7 +23781,7 @@
       <c r="E21" s="61"/>
       <c r="F21" s="61"/>
     </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="7" t="s">
         <v>343</v>
       </c>
@@ -23817,7 +23800,7 @@
       <c r="L22" s="47"/>
       <c r="M22" s="47"/>
     </row>
-    <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="126"/>
       <c r="B23" s="139"/>
       <c r="C23" s="139"/>
@@ -23832,7 +23815,7 @@
       <c r="L23" s="108"/>
       <c r="M23" s="108"/>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="17" t="s">
         <v>169</v>
@@ -23845,7 +23828,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="17" t="s">
         <v>170</v>
@@ -23858,7 +23841,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="17" t="s">
         <v>171</v>
@@ -23871,7 +23854,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="17" t="s">
         <v>172</v>
@@ -23884,7 +23867,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="17" t="s">
         <v>173</v>
@@ -23897,7 +23880,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="17" t="s">
         <v>174</v>
@@ -23910,7 +23893,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="17" t="s">
         <v>175</v>
@@ -23923,7 +23906,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="17" t="s">
         <v>176</v>
@@ -23936,7 +23919,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -23944,7 +23927,7 @@
       <c r="E32" s="61"/>
       <c r="F32" s="61"/>
     </row>
-    <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="7" t="s">
         <v>343</v>
       </c>
@@ -23963,7 +23946,7 @@
       <c r="L33" s="47"/>
       <c r="M33" s="47"/>
     </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="126"/>
       <c r="B34" s="139"/>
       <c r="C34" s="139"/>
@@ -23978,7 +23961,7 @@
       <c r="L34" s="108"/>
       <c r="M34" s="108"/>
     </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="17" t="s">
         <v>178</v>
@@ -23991,7 +23974,7 @@
         <v>-4.84</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="17" t="s">
         <v>179</v>
@@ -24004,7 +23987,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="17" t="s">
         <v>180</v>
@@ -24017,7 +24000,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="17" t="s">
         <v>181</v>
@@ -24030,7 +24013,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="17" t="s">
         <v>182</v>
@@ -24043,7 +24026,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="17" t="s">
         <v>183</v>
@@ -24056,7 +24039,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="17" t="s">
         <v>184</v>
@@ -24069,7 +24052,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="17" t="s">
         <v>185</v>
@@ -24082,7 +24065,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="17" t="s">
         <v>186</v>
@@ -24095,7 +24078,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -24103,7 +24086,7 @@
       <c r="E44" s="61"/>
       <c r="F44" s="61"/>
     </row>
-    <row r="45" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="7" t="s">
         <v>343</v>
       </c>
@@ -24125,7 +24108,7 @@
       <c r="L45" s="47"/>
       <c r="M45" s="47"/>
     </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -24133,7 +24116,7 @@
       <c r="E46" s="59"/>
       <c r="F46" s="22"/>
     </row>
-    <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="7" t="s">
         <v>343</v>
       </c>
@@ -24152,7 +24135,7 @@
       <c r="L47" s="47"/>
       <c r="M47" s="47"/>
     </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="14" t="s">
         <v>189</v>
@@ -24165,7 +24148,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -24173,7 +24156,7 @@
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
     </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="62" t="s">
         <v>190</v>
@@ -24183,7 +24166,7 @@
       <c r="E50" s="61"/>
       <c r="F50" s="61"/>
     </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="63" t="s">
         <v>191</v>
@@ -24193,7 +24176,7 @@
       <c r="E51" s="61"/>
       <c r="F51" s="61"/>
     </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -24201,7 +24184,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
     </row>
-    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="18" t="s">
         <v>192</v>
@@ -24211,7 +24194,7 @@
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
     </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -24219,7 +24202,7 @@
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
     </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="33" t="s">
         <v>339</v>
@@ -24236,7 +24219,7 @@
       <c r="L55" s="34"/>
       <c r="M55" s="34"/>
     </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="33" t="s">
         <v>86</v>
@@ -24253,7 +24236,7 @@
       <c r="L56" s="34"/>
       <c r="M56" s="34"/>
     </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="33" t="s">
         <v>340</v>
@@ -24270,267 +24253,267 @@
       <c r="L57" s="34"/>
       <c r="M57" s="34"/>
     </row>
-    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="51"/>
       <c r="C58" s="51"/>
     </row>
-    <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="51"/>
       <c r="C59" s="51"/>
     </row>
-    <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="51"/>
       <c r="C60" s="51"/>
     </row>
-    <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="51"/>
       <c r="C61" s="51"/>
     </row>
-    <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="51"/>
       <c r="C62" s="51"/>
     </row>
-    <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="51"/>
       <c r="C63" s="51"/>
     </row>
-    <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="51"/>
       <c r="C64" s="51"/>
     </row>
-    <row r="65" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="51"/>
       <c r="C65" s="51"/>
     </row>
-    <row r="66" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="51"/>
       <c r="C66" s="51"/>
     </row>
-    <row r="67" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="51"/>
       <c r="C67" s="51"/>
     </row>
-    <row r="68" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="51"/>
       <c r="C68" s="51"/>
     </row>
-    <row r="69" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="51"/>
       <c r="C69" s="51"/>
     </row>
-    <row r="70" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="51"/>
       <c r="C70" s="51"/>
     </row>
-    <row r="71" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
       <c r="C71" s="51"/>
     </row>
-    <row r="72" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
       <c r="C72" s="51"/>
     </row>
-    <row r="73" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="51"/>
       <c r="C73" s="51"/>
     </row>
-    <row r="74" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="51"/>
       <c r="C74" s="51"/>
     </row>
-    <row r="75" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="51"/>
       <c r="C75" s="51"/>
     </row>
-    <row r="76" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="51"/>
       <c r="C76" s="51"/>
     </row>
-    <row r="77" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="51"/>
       <c r="C77" s="51"/>
     </row>
-    <row r="78" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="51"/>
       <c r="C78" s="51"/>
     </row>
-    <row r="79" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="51"/>
       <c r="C79" s="51"/>
     </row>
-    <row r="80" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="51"/>
       <c r="C80" s="51"/>
     </row>
-    <row r="81" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="51"/>
       <c r="C81" s="51"/>
     </row>
-    <row r="82" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="51"/>
       <c r="C82" s="51"/>
     </row>
-    <row r="83" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="51"/>
       <c r="C83" s="51"/>
     </row>
-    <row r="84" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="51"/>
       <c r="C84" s="51"/>
     </row>
-    <row r="85" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="51"/>
       <c r="C85" s="51"/>
     </row>
-    <row r="86" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="51"/>
       <c r="C86" s="51"/>
     </row>
-    <row r="87" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="51"/>
       <c r="C87" s="51"/>
     </row>
-    <row r="88" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="51"/>
       <c r="C88" s="51"/>
     </row>
-    <row r="89" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="51"/>
       <c r="C89" s="51"/>
     </row>
-    <row r="90" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="51"/>
       <c r="C90" s="51"/>
     </row>
-    <row r="91" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="51"/>
       <c r="C91" s="51"/>
     </row>
-    <row r="92" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
     </row>
-    <row r="93" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="51"/>
       <c r="C93" s="51"/>
     </row>
-    <row r="94" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="51"/>
       <c r="C94" s="51"/>
     </row>
-    <row r="95" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="51"/>
       <c r="C95" s="51"/>
     </row>
-    <row r="96" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
       <c r="C96" s="51"/>
     </row>
-    <row r="97" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51"/>
       <c r="C97" s="51"/>
     </row>
-    <row r="98" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
       <c r="C98" s="51"/>
     </row>
-    <row r="99" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
       <c r="C99" s="51"/>
     </row>
-    <row r="100" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
       <c r="C100" s="51"/>
     </row>
-    <row r="101" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
       <c r="C101" s="51"/>
     </row>
-    <row r="102" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
       <c r="C102" s="51"/>
     </row>
-    <row r="103" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
       <c r="C103" s="51"/>
     </row>
-    <row r="104" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
       <c r="C104" s="51"/>
     </row>
-    <row r="105" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
       <c r="C105" s="51"/>
     </row>
-    <row r="106" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
       <c r="C106" s="51"/>
     </row>
-    <row r="107" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
       <c r="C107" s="51"/>
     </row>
-    <row r="108" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
       <c r="C108" s="51"/>
     </row>
-    <row r="109" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
       <c r="C109" s="51"/>
     </row>
-    <row r="110" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
       <c r="C110" s="51"/>
     </row>
-    <row r="111" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
       <c r="C111" s="51"/>
     </row>
-    <row r="112" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
       <c r="C112" s="51"/>
     </row>
-    <row r="113" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
       <c r="C113" s="51"/>
     </row>
-    <row r="114" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
       <c r="C114" s="51"/>
     </row>
-    <row r="115" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
       <c r="C115" s="51"/>
     </row>
-    <row r="116" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
       <c r="C116" s="51"/>
     </row>
-    <row r="117" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
       <c r="C117" s="51"/>
     </row>
-    <row r="118" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
       <c r="C118" s="51"/>
     </row>
-    <row r="119" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
       <c r="C119" s="51"/>
     </row>
-    <row r="120" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
       <c r="C120" s="51"/>
     </row>
-    <row r="121" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="51"/>
       <c r="C121" s="51"/>
     </row>
-    <row r="122" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="51"/>
       <c r="C122" s="51"/>
     </row>
-    <row r="123" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="51"/>
       <c r="C123" s="51"/>
     </row>
@@ -24608,15 +24591,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="49.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="14" width="11" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="6"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -24636,7 +24619,7 @@
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -24652,7 +24635,7 @@
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
     </row>
-    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="7" t="s">
         <v>343</v>
       </c>
@@ -24672,7 +24655,7 @@
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>343</v>
       </c>
@@ -24692,7 +24675,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>343</v>
       </c>
@@ -24724,29 +24707,29 @@
       </c>
       <c r="I5" s="24" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="J5" s="24" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="K5" s="24" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="L5" s="24" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="M5" s="24" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
+        <v>5F</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="14"/>
       <c r="C6" s="3"/>
@@ -24762,7 +24745,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
     </row>
-    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
         <v>343</v>
       </c>
@@ -24782,7 +24765,7 @@
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
     </row>
-    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="142"/>
       <c r="B8" s="143"/>
       <c r="C8" s="142"/>
@@ -24798,7 +24781,7 @@
       <c r="M8" s="144"/>
       <c r="N8" s="144"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -24846,7 +24829,7 @@
       </c>
       <c r="N9" s="252"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>165</v>
@@ -24894,7 +24877,7 @@
       </c>
       <c r="N10" s="253"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="58" t="s">
         <v>7</v>
@@ -24942,7 +24925,7 @@
       </c>
       <c r="N11" s="254"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="147"/>
       <c r="B12" s="148"/>
       <c r="C12" s="149"/>
@@ -24958,7 +24941,7 @@
       <c r="M12" s="151"/>
       <c r="N12" s="151"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="17" t="s">
         <v>196</v>
@@ -25006,7 +24989,7 @@
       </c>
       <c r="N13" s="252"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="17" t="s">
         <v>9</v>
@@ -25054,7 +25037,7 @@
       </c>
       <c r="N14" s="253"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="58" t="s">
         <v>18</v>
@@ -25102,7 +25085,7 @@
       </c>
       <c r="N15" s="254"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="147"/>
       <c r="B16" s="148"/>
       <c r="C16" s="149"/>
@@ -25118,7 +25101,7 @@
       <c r="M16" s="151"/>
       <c r="N16" s="151"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="17" t="s">
         <v>10</v>
@@ -25166,7 +25149,7 @@
       </c>
       <c r="N17" s="253"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="58" t="s">
         <v>11</v>
@@ -25214,7 +25197,7 @@
       </c>
       <c r="N18" s="254"/>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="147"/>
       <c r="B19" s="148"/>
       <c r="C19" s="149"/>
@@ -25230,7 +25213,7 @@
       <c r="M19" s="151"/>
       <c r="N19" s="151"/>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="17" t="s">
         <v>12</v>
@@ -25278,7 +25261,7 @@
       </c>
       <c r="N20" s="253"/>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="58" t="s">
         <v>14</v>
@@ -25326,7 +25309,7 @@
       </c>
       <c r="N21" s="254"/>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="147"/>
       <c r="B22" s="148"/>
       <c r="C22" s="149"/>
@@ -25342,7 +25325,7 @@
       <c r="M22" s="151"/>
       <c r="N22" s="151"/>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="17" t="s">
         <v>197</v>
@@ -25390,7 +25373,7 @@
       </c>
       <c r="N23" s="252"/>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3"/>
       <c r="B24" s="58" t="s">
         <v>16</v>
@@ -25438,7 +25421,7 @@
       </c>
       <c r="N24" s="255"/>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="14"/>
       <c r="C25" s="9"/>
@@ -25454,7 +25437,7 @@
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
     </row>
-    <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="7" t="s">
         <v>343</v>
       </c>
@@ -25474,7 +25457,7 @@
       <c r="M26" s="23"/>
       <c r="N26" s="23"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="17" t="s">
         <v>1</v>
@@ -25492,7 +25475,7 @@
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>343</v>
       </c>
@@ -25507,27 +25490,27 @@
       <c r="H28" s="24"/>
       <c r="I28" s="24" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="J28" s="24" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="K28" s="24" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="L28" s="24" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="M28" s="24" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
+        <v>5F</v>
       </c>
       <c r="N28" s="234"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="17" t="s">
         <v>200</v>
@@ -25569,7 +25552,7 @@
       </c>
       <c r="N29" s="256"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="17" t="s">
         <v>201</v>
@@ -25611,7 +25594,7 @@
       </c>
       <c r="N30" s="256"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="17" t="s">
         <v>202</v>
@@ -25653,7 +25636,7 @@
       </c>
       <c r="N31" s="256"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="17" t="s">
         <v>203</v>
@@ -25695,7 +25678,7 @@
       </c>
       <c r="N32" s="256"/>
     </row>
-    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="17" t="s">
         <v>204</v>
@@ -25737,7 +25720,7 @@
       </c>
       <c r="N33" s="256"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="17" t="s">
         <v>205</v>
@@ -25779,7 +25762,7 @@
       </c>
       <c r="N34" s="256"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="14"/>
       <c r="C35" s="9"/>
@@ -25795,7 +25778,7 @@
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
     </row>
-    <row r="36" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="7" t="s">
         <v>343</v>
       </c>
@@ -25815,7 +25798,7 @@
       <c r="M36" s="23"/>
       <c r="N36" s="23"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="17" t="s">
         <v>214</v>
@@ -25857,7 +25840,7 @@
       </c>
       <c r="N37" s="256"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="17" t="s">
         <v>215</v>
@@ -25899,7 +25882,7 @@
       </c>
       <c r="N38" s="256"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="17"/>
       <c r="C39" s="9"/>
@@ -25915,7 +25898,7 @@
       <c r="M39" s="22"/>
       <c r="N39" s="22"/>
     </row>
-    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="7"/>
       <c r="B40" s="53" t="s">
         <v>206</v>
@@ -25933,7 +25916,7 @@
       <c r="M40" s="23"/>
       <c r="N40" s="23"/>
     </row>
-    <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="141"/>
       <c r="B41" s="152"/>
       <c r="C41" s="153"/>
@@ -25949,7 +25932,7 @@
       <c r="M41" s="120"/>
       <c r="N41" s="120"/>
     </row>
-    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="17" t="s">
         <v>134</v>
@@ -25997,7 +25980,7 @@
       </c>
       <c r="N42" s="252"/>
     </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="17" t="s">
         <v>207</v>
@@ -26045,7 +26028,7 @@
       </c>
       <c r="N43" s="253"/>
     </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="58" t="s">
         <v>208</v>
@@ -26093,7 +26076,7 @@
       </c>
       <c r="N44" s="254"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="81"/>
       <c r="B45" s="145"/>
       <c r="C45" s="101"/>
@@ -26109,7 +26092,7 @@
       <c r="M45" s="67"/>
       <c r="N45" s="67"/>
     </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="17" t="s">
         <v>209</v>
@@ -26157,7 +26140,7 @@
       </c>
       <c r="N46" s="252"/>
     </row>
-    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="17" t="s">
         <v>210</v>
@@ -26205,7 +26188,7 @@
       </c>
       <c r="N47" s="252"/>
     </row>
-    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="17" t="s">
         <v>211</v>
@@ -26253,7 +26236,7 @@
       </c>
       <c r="N48" s="252"/>
     </row>
-    <row r="49" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="81"/>
       <c r="B49" s="92" t="s">
         <v>212</v>
@@ -26301,7 +26284,7 @@
       </c>
       <c r="N49" s="257"/>
     </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="14"/>
       <c r="C50" s="9"/>
@@ -26317,7 +26300,7 @@
       <c r="M50" s="22"/>
       <c r="N50" s="22"/>
     </row>
-    <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="7"/>
       <c r="B51" s="53" t="s">
         <v>216</v>
@@ -26335,7 +26318,7 @@
       <c r="M51" s="23"/>
       <c r="N51" s="23"/>
     </row>
-    <row r="52" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="141"/>
       <c r="B52" s="152"/>
       <c r="C52" s="153"/>
@@ -26351,7 +26334,7 @@
       <c r="M52" s="120"/>
       <c r="N52" s="120"/>
     </row>
-    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="17" t="s">
         <v>217</v>
@@ -26372,7 +26355,7 @@
       <c r="M53" s="414"/>
       <c r="N53" s="414"/>
     </row>
-    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="17" t="s">
         <v>62</v>
@@ -26393,7 +26376,7 @@
       <c r="M54" s="414"/>
       <c r="N54" s="414"/>
     </row>
-    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="17" t="s">
         <v>66</v>
@@ -26414,7 +26397,7 @@
       <c r="M55" s="414"/>
       <c r="N55" s="414"/>
     </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="58" t="s">
         <v>67</v>
@@ -26435,7 +26418,7 @@
       <c r="M56" s="415"/>
       <c r="N56" s="415"/>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="17"/>
       <c r="C57" s="9"/>
@@ -26451,7 +26434,7 @@
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
     </row>
-    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="17" t="s">
         <v>218</v>
@@ -26472,7 +26455,7 @@
       <c r="M58" s="414"/>
       <c r="N58" s="414"/>
     </row>
-    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="17" t="s">
         <v>219</v>
@@ -26493,7 +26476,7 @@
       <c r="M59" s="414"/>
       <c r="N59" s="414"/>
     </row>
-    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="17" t="s">
         <v>220</v>
@@ -26514,7 +26497,7 @@
       <c r="M60" s="414"/>
       <c r="N60" s="414"/>
     </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="17" t="s">
         <v>69</v>
@@ -26535,7 +26518,7 @@
       <c r="M61" s="414"/>
       <c r="N61" s="414"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="17" t="s">
         <v>70</v>
@@ -26556,7 +26539,7 @@
       <c r="M62" s="414"/>
       <c r="N62" s="414"/>
     </row>
-    <row r="63" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3"/>
       <c r="B63" s="55" t="s">
         <v>73</v>
@@ -26577,7 +26560,7 @@
       <c r="M63" s="415"/>
       <c r="N63" s="415"/>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="14"/>
       <c r="C64" s="9"/>
@@ -26593,7 +26576,7 @@
       <c r="M64" s="22"/>
       <c r="N64" s="22"/>
     </row>
-    <row r="65" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="7"/>
       <c r="B65" s="53" t="s">
         <v>221</v>
@@ -26611,7 +26594,7 @@
       <c r="M65" s="23"/>
       <c r="N65" s="23"/>
     </row>
-    <row r="66" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="141"/>
       <c r="B66" s="152"/>
       <c r="C66" s="153"/>
@@ -26627,7 +26610,7 @@
       <c r="M66" s="120"/>
       <c r="N66" s="120"/>
     </row>
-    <row r="67" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="17" t="s">
         <v>222</v>
@@ -26648,7 +26631,7 @@
       <c r="M67" s="414"/>
       <c r="N67" s="414"/>
     </row>
-    <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="17" t="s">
         <v>73</v>
@@ -26669,7 +26652,7 @@
       <c r="M68" s="414"/>
       <c r="N68" s="414"/>
     </row>
-    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="17" t="s">
         <v>223</v>
@@ -26690,7 +26673,7 @@
       <c r="M69" s="414"/>
       <c r="N69" s="414"/>
     </row>
-    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="17" t="s">
         <v>224</v>
@@ -26711,7 +26694,7 @@
       <c r="M70" s="414"/>
       <c r="N70" s="414"/>
     </row>
-    <row r="71" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3"/>
       <c r="B71" s="58" t="s">
         <v>225</v>
@@ -26732,7 +26715,7 @@
       <c r="M71" s="415"/>
       <c r="N71" s="415"/>
     </row>
-    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="17" t="s">
         <v>226</v>
@@ -26753,7 +26736,7 @@
       <c r="M72" s="414"/>
       <c r="N72" s="414"/>
     </row>
-    <row r="73" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="14"/>
       <c r="C73" s="9"/>
@@ -26769,7 +26752,7 @@
       <c r="M73" s="22"/>
       <c r="N73" s="22"/>
     </row>
-    <row r="74" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="14" t="s">
         <v>227</v>
@@ -26802,7 +26785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="14" t="s">
         <v>228</v>
@@ -26841,7 +26824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="14" t="s">
         <v>229</v>
@@ -26877,7 +26860,7 @@
       </c>
       <c r="N76" s="37"/>
     </row>
-    <row r="77" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="14" t="s">
         <v>230</v>
@@ -26898,7 +26881,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="14" t="s">
         <v>231</v>
@@ -26934,7 +26917,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="14"/>
       <c r="C79" s="9"/>
@@ -26950,7 +26933,7 @@
       <c r="M79" s="22"/>
       <c r="N79" s="22"/>
     </row>
-    <row r="80" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A80" s="7"/>
       <c r="B80" s="53" t="s">
         <v>232</v>
@@ -26968,7 +26951,7 @@
       <c r="M80" s="23"/>
       <c r="N80" s="23"/>
     </row>
-    <row r="81" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="141"/>
       <c r="B81" s="152"/>
       <c r="C81" s="153"/>
@@ -26984,7 +26967,7 @@
       <c r="M81" s="120"/>
       <c r="N81" s="120"/>
     </row>
-    <row r="82" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="58" t="s">
         <v>233</v>
@@ -27005,7 +26988,7 @@
       <c r="M82" s="414"/>
       <c r="N82" s="414"/>
     </row>
-    <row r="83" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="17" t="s">
         <v>234</v>
@@ -27026,7 +27009,7 @@
       <c r="M83" s="414"/>
       <c r="N83" s="414"/>
     </row>
-    <row r="84" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="58" t="s">
         <v>61</v>
@@ -27047,7 +27030,7 @@
       <c r="M84" s="415"/>
       <c r="N84" s="415"/>
     </row>
-    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="81"/>
       <c r="B85" s="145"/>
       <c r="C85" s="101"/>
@@ -27063,7 +27046,7 @@
       <c r="M85" s="416"/>
       <c r="N85" s="416"/>
     </row>
-    <row r="86" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="17" t="s">
         <v>235</v>
@@ -27084,7 +27067,7 @@
       <c r="M86" s="414"/>
       <c r="N86" s="414"/>
     </row>
-    <row r="87" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="17" t="s">
         <v>236</v>
@@ -27105,7 +27088,7 @@
       <c r="M87" s="414"/>
       <c r="N87" s="414"/>
     </row>
-    <row r="88" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3"/>
       <c r="B88" s="58" t="s">
         <v>237</v>
@@ -27126,7 +27109,7 @@
       <c r="M88" s="415"/>
       <c r="N88" s="415"/>
     </row>
-    <row r="89" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="81"/>
       <c r="B89" s="145"/>
       <c r="C89" s="101"/>
@@ -27142,7 +27125,7 @@
       <c r="M89" s="416"/>
       <c r="N89" s="416"/>
     </row>
-    <row r="90" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="17" t="s">
         <v>59</v>
@@ -27163,7 +27146,7 @@
       <c r="M90" s="414"/>
       <c r="N90" s="414"/>
     </row>
-    <row r="91" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3"/>
       <c r="B91" s="58" t="s">
         <v>238</v>
@@ -27184,7 +27167,7 @@
       <c r="M91" s="415"/>
       <c r="N91" s="415"/>
     </row>
-    <row r="92" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="17" t="s">
         <v>239</v>
@@ -27207,7 +27190,7 @@
       <c r="M92" s="414"/>
       <c r="N92" s="414"/>
     </row>
-    <row r="93" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="17" t="s">
         <v>240</v>
@@ -27230,7 +27213,7 @@
       <c r="M93" s="414"/>
       <c r="N93" s="414"/>
     </row>
-    <row r="94" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="115" t="s">
         <v>345</v>
@@ -27253,7 +27236,7 @@
       <c r="M94" s="414"/>
       <c r="N94" s="414"/>
     </row>
-    <row r="95" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="115"/>
       <c r="C95" s="116"/>
@@ -27269,7 +27252,7 @@
       <c r="M95" s="22"/>
       <c r="N95" s="22"/>
     </row>
-    <row r="96" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A96" s="7"/>
       <c r="B96" s="53" t="s">
         <v>241</v>
@@ -27287,7 +27270,7 @@
       <c r="M96" s="23"/>
       <c r="N96" s="23"/>
     </row>
-    <row r="97" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="16" t="s">
         <v>242</v>
@@ -27317,7 +27300,7 @@
       <c r="M97" s="24"/>
       <c r="N97" s="24"/>
     </row>
-    <row r="98" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="14"/>
       <c r="C98" s="327">
@@ -27351,7 +27334,7 @@
       <c r="M98" s="22"/>
       <c r="N98" s="22"/>
     </row>
-    <row r="99" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="14"/>
       <c r="C99" s="327">
@@ -27385,7 +27368,7 @@
       <c r="M99" s="22"/>
       <c r="N99" s="22"/>
     </row>
-    <row r="100" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="14"/>
       <c r="C100" s="328">
@@ -27419,7 +27402,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
     </row>
-    <row r="101" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="14"/>
       <c r="C101" s="327">
@@ -27453,7 +27436,7 @@
       <c r="M101" s="22"/>
       <c r="N101" s="22"/>
     </row>
-    <row r="102" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="14"/>
       <c r="C102" s="327">
@@ -27487,7 +27470,7 @@
       <c r="M102" s="22"/>
       <c r="N102" s="22"/>
     </row>
-    <row r="103" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="18" t="s">
         <v>244</v>
@@ -27505,7 +27488,7 @@
       <c r="M103" s="22"/>
       <c r="N103" s="22"/>
     </row>
-    <row r="104" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="14"/>
       <c r="C104" s="9"/>
@@ -27521,7 +27504,7 @@
       <c r="M104" s="22"/>
       <c r="N104" s="22"/>
     </row>
-    <row r="105" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A105" s="7"/>
       <c r="B105" s="53" t="s">
         <v>245</v>
@@ -27539,7 +27522,7 @@
       <c r="M105" s="23"/>
       <c r="N105" s="23"/>
     </row>
-    <row r="106" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="16" t="s">
         <v>2</v>
@@ -27565,7 +27548,7 @@
       <c r="M106" s="24"/>
       <c r="N106"/>
     </row>
-    <row r="107" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="17" t="s">
         <v>249</v>
@@ -27597,7 +27580,7 @@
       <c r="M107" s="22"/>
       <c r="N107"/>
     </row>
-    <row r="108" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="17" t="s">
         <v>96</v>
@@ -27629,7 +27612,7 @@
       <c r="M108" s="22"/>
       <c r="N108"/>
     </row>
-    <row r="109" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="17" t="s">
         <v>74</v>
@@ -27661,7 +27644,7 @@
       <c r="M109" s="22"/>
       <c r="N109"/>
     </row>
-    <row r="110" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="17" t="s">
         <v>73</v>
@@ -27693,7 +27676,7 @@
       <c r="M110" s="22"/>
       <c r="N110"/>
     </row>
-    <row r="111" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="17" t="s">
         <v>250</v>
@@ -27725,7 +27708,7 @@
       <c r="M111" s="22"/>
       <c r="N111"/>
     </row>
-    <row r="112" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="14"/>
       <c r="C112" s="9"/>
@@ -27741,7 +27724,7 @@
       <c r="M112" s="22"/>
       <c r="N112" s="22"/>
     </row>
-    <row r="113" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="33" t="s">
         <v>339</v>
@@ -27759,7 +27742,7 @@
       <c r="M113" s="34"/>
       <c r="N113" s="34"/>
     </row>
-    <row r="114" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="33" t="s">
         <v>86</v>
@@ -27777,7 +27760,7 @@
       <c r="M114" s="34"/>
       <c r="N114" s="34"/>
     </row>
-    <row r="115" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="33" t="s">
         <v>340</v>
@@ -27795,33 +27778,33 @@
       <c r="M115" s="34"/>
       <c r="N115" s="34"/>
     </row>
-    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="100"/>
       <c r="B117" s="103" t="s">
         <v>336</v>
       </c>
       <c r="C117" s="103" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="D117" s="103" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="E117" s="103" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="F117" s="103" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="G117" s="103" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
+        <v>5F</v>
       </c>
       <c r="H117" s="102"/>
       <c r="I117" s="102"/>
@@ -27831,7 +27814,7 @@
       <c r="M117" s="102"/>
       <c r="N117" s="102"/>
     </row>
-    <row r="118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51" t="s">
         <v>337</v>
       </c>
@@ -27863,27 +27846,27 @@
       <c r="M118" s="102"/>
       <c r="N118" s="102"/>
     </row>
-    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
       <c r="C119" s="287" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="D119" s="287" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="E119" s="287" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="F119" s="287" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="G119" s="287" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
+        <v>5F</v>
       </c>
       <c r="H119" s="102"/>
       <c r="I119" s="102"/>
@@ -27893,7 +27876,7 @@
       <c r="M119" s="102"/>
       <c r="N119" s="102"/>
     </row>
-    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="100"/>
       <c r="B120" s="103" t="s">
         <v>338</v>
@@ -27926,7 +27909,7 @@
       <c r="M120" s="102"/>
       <c r="N120" s="102"/>
     </row>
-    <row r="121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="51" t="s">
         <v>5</v>
       </c>
@@ -27958,13 +27941,13 @@
       <c r="M121" s="102"/>
       <c r="N121" s="102"/>
     </row>
-    <row r="122" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="51"/>
     </row>
-    <row r="123" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="51"/>
     </row>
-    <row r="124" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="51"/>
     </row>
   </sheetData>
@@ -28142,19 +28125,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="21" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" customWidth="1"/>
+    <col min="2" max="2" width="34.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
+    <col min="5" max="6" width="14.44140625" style="21" customWidth="1"/>
     <col min="7" max="11" width="12" style="21" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="21" customWidth="1"/>
-    <col min="13" max="14" width="11.5703125" style="21"/>
+    <col min="12" max="12" width="16.88671875" style="21" customWidth="1"/>
+    <col min="13" max="14" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="250"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -28175,7 +28158,7 @@
       <c r="N1" s="264"/>
       <c r="O1" s="264"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -28189,7 +28172,7 @@
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
     </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="126" t="s">
         <v>343</v>
       </c>
@@ -28209,7 +28192,7 @@
       <c r="M3" s="108"/>
       <c r="N3" s="108"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="12" t="s">
         <v>252</v>
@@ -28225,7 +28208,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="14"/>
       <c r="C5" s="3"/>
@@ -28239,7 +28222,7 @@
       <c r="K5" s="22"/>
       <c r="L5" s="22"/>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="126" t="s">
         <v>343</v>
       </c>
@@ -28259,7 +28242,7 @@
       <c r="M6" s="108"/>
       <c r="N6" s="108"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="251"/>
       <c r="B7" s="16"/>
       <c r="C7" s="1"/>
@@ -28292,7 +28275,7 @@
       </c>
       <c r="M7" s="251"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="263"/>
       <c r="B8" s="28" t="s">
         <v>263</v>
@@ -28328,7 +28311,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="41" t="s">
         <v>267</v>
@@ -28355,7 +28338,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="41" t="s">
         <v>269</v>
@@ -28382,7 +28365,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="41" t="s">
         <v>271</v>
@@ -28409,7 +28392,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="41" t="s">
         <v>273</v>
@@ -28436,7 +28419,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="41" t="s">
         <v>275</v>
@@ -28463,7 +28446,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="14"/>
       <c r="C14" s="9"/>
@@ -28477,7 +28460,7 @@
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="14" t="s">
         <v>277</v>
@@ -28520,7 +28503,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="14" t="s">
         <v>278</v>
@@ -28563,7 +28546,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="14" t="s">
         <v>279</v>
@@ -28606,7 +28589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="14" t="s">
         <v>280</v>
@@ -28649,7 +28632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="14"/>
       <c r="C19" s="9"/>
@@ -28663,7 +28646,7 @@
       <c r="K19" s="22"/>
       <c r="L19" s="22"/>
     </row>
-    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="126" t="s">
         <v>343</v>
       </c>
@@ -28683,7 +28666,7 @@
       <c r="M20" s="108"/>
       <c r="N20" s="108"/>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="251"/>
       <c r="B21" s="52" t="s">
         <v>282</v>
@@ -28691,7 +28674,7 @@
       <c r="C21" s="10"/>
       <c r="D21" s="24" t="str">
         <f>INPUT!D117&amp;" (LTM)"</f>
-        <v>2025 (LTM)</v>
+        <v xml:space="preserve"> (LTM)</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -28704,7 +28687,7 @@
       <c r="M21" s="251"/>
       <c r="N21" s="251"/>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="17" t="s">
         <v>283</v>
@@ -28725,7 +28708,7 @@
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="17" t="s">
         <v>284</v>
@@ -28746,7 +28729,7 @@
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="17" t="s">
         <v>285</v>
@@ -28767,7 +28750,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="17" t="s">
         <v>286</v>
@@ -28788,7 +28771,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="17" t="s">
         <v>287</v>
@@ -28809,7 +28792,7 @@
       <c r="K26" s="72"/>
       <c r="L26" s="72"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="14"/>
       <c r="C27" s="9"/>
@@ -28823,7 +28806,7 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="126" t="s">
         <v>343</v>
       </c>
@@ -28843,7 +28826,7 @@
       <c r="M28" s="108"/>
       <c r="N28" s="108"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="17" t="s">
         <v>290</v>
@@ -28871,7 +28854,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="17" t="s">
         <v>291</v>
@@ -28899,7 +28882,7 @@
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="17" t="s">
         <v>292</v>
@@ -28927,7 +28910,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="17"/>
       <c r="C32" s="9"/>
@@ -28941,7 +28924,7 @@
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
     </row>
-    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="17" t="s">
         <v>293</v>
@@ -28971,7 +28954,7 @@
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="17" t="s">
         <v>294</v>
@@ -29001,7 +28984,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="17" t="s">
         <v>295</v>
@@ -29031,7 +29014,7 @@
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
     </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3"/>
       <c r="B36" s="58" t="s">
         <v>250</v>
@@ -29061,7 +29044,7 @@
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="17" t="s">
         <v>296</v>
@@ -29091,7 +29074,7 @@
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3"/>
       <c r="B38" s="58" t="s">
         <v>297</v>
@@ -29121,7 +29104,7 @@
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="17"/>
       <c r="C39" s="9"/>
@@ -29135,7 +29118,7 @@
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
     </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="18" t="s">
         <v>298</v>
@@ -29151,7 +29134,7 @@
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
     </row>
-    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="14"/>
       <c r="C41" s="3"/>
@@ -29165,7 +29148,7 @@
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
     </row>
-    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="250"/>
       <c r="B42" s="33" t="s">
         <v>339</v>
@@ -29183,7 +29166,7 @@
       <c r="M42" s="264"/>
       <c r="N42" s="264"/>
     </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="250"/>
       <c r="B43" s="33" t="s">
         <v>86</v>
@@ -29201,7 +29184,7 @@
       <c r="M43" s="264"/>
       <c r="N43" s="264"/>
     </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="250"/>
       <c r="B44" s="33" t="s">
         <v>340</v>
@@ -29219,10 +29202,10 @@
       <c r="M44" s="264"/>
       <c r="N44" s="264"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="51"/>
     </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="111"/>
       <c r="B46" s="105" t="s">
         <v>333</v>
@@ -29244,7 +29227,7 @@
       <c r="M46" s="265"/>
       <c r="N46" s="265"/>
     </row>
-    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="354" t="str">
         <f>B9</f>
         <v>Peer Company 1</v>
@@ -29258,7 +29241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="354" t="str">
         <f>B10</f>
         <v>Peer Company 2</v>
@@ -29272,7 +29255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="354" t="str">
         <f>B11</f>
         <v>Peer Company 3</v>
@@ -29286,7 +29269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="354" t="str">
         <f>B12</f>
         <v>Peer Company 4</v>
@@ -29300,7 +29283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="354" t="str">
         <f>B13</f>
         <v>Peer Company 5</v>
@@ -29314,7 +29297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="354" t="str">
         <f>B15</f>
         <v>Mean</v>
@@ -29328,211 +29311,211 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="51"/>
     </row>
-    <row r="54" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="51"/>
     </row>
-    <row r="55" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="51"/>
     </row>
-    <row r="56" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="51"/>
       <c r="F56" s="21" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="51"/>
     </row>
-    <row r="58" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="51"/>
     </row>
-    <row r="59" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="51"/>
     </row>
-    <row r="60" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="51"/>
     </row>
-    <row r="61" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="51"/>
     </row>
-    <row r="62" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="51"/>
     </row>
-    <row r="63" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="51"/>
     </row>
-    <row r="64" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="51"/>
     </row>
-    <row r="65" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="51"/>
     </row>
-    <row r="66" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="51"/>
     </row>
-    <row r="67" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="51"/>
     </row>
-    <row r="68" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="51"/>
     </row>
-    <row r="69" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="51"/>
     </row>
-    <row r="70" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="51"/>
     </row>
-    <row r="71" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
     </row>
-    <row r="72" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
     </row>
-    <row r="73" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="51"/>
     </row>
-    <row r="74" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="51"/>
     </row>
-    <row r="75" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="51"/>
     </row>
-    <row r="76" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="51"/>
     </row>
-    <row r="77" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="51"/>
     </row>
-    <row r="78" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="51"/>
     </row>
-    <row r="79" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="51"/>
     </row>
-    <row r="80" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="51"/>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="51"/>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="51"/>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="51"/>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="51"/>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="51"/>
     </row>
-    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="51"/>
     </row>
-    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="51"/>
     </row>
-    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="51"/>
     </row>
-    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="51"/>
     </row>
-    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="51"/>
     </row>
-    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="51"/>
     </row>
-    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="51"/>
     </row>
-    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="51"/>
     </row>
-    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="51"/>
     </row>
-    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="51"/>
     </row>
-    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51"/>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
     </row>
-    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
     </row>
-    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
     </row>
-    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
     </row>
-    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
     </row>
-    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
     </row>
-    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
     </row>
-    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
     </row>
-    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
     </row>
-    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
     </row>
-    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
     </row>
-    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
     </row>
-    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
     </row>
-    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
     </row>
-    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
     </row>
-    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
     </row>
-    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
     </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
     </row>
   </sheetData>
@@ -29549,17 +29532,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="248" customWidth="1"/>
     <col min="2" max="2" width="51" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="9" width="13.28515625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="9" width="13.33203125" style="21" customWidth="1"/>
     <col min="10" max="13" width="11" style="21" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="110"/>
+    <col min="14" max="14" width="11.44140625" style="110"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54.95" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" ht="54.9" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="243"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -29579,7 +29562,7 @@
       <c r="M1" s="29"/>
       <c r="N1" s="109"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="244"/>
       <c r="B2" s="14"/>
       <c r="C2" s="3"/>
@@ -29594,7 +29577,7 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
     </row>
-    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="245" t="s">
         <v>343</v>
       </c>
@@ -29613,7 +29596,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="244"/>
       <c r="B4" s="12" t="s">
         <v>300</v>
@@ -29630,7 +29613,7 @@
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="246" t="s">
         <v>343</v>
       </c>
@@ -29642,46 +29625,46 @@
       </c>
       <c r="D5" s="16">
         <f>INPUT!D117</f>
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="E5" s="16">
         <f>INPUT!D117-3</f>
-        <v>2022</v>
+        <v>-3</v>
       </c>
       <c r="F5" s="16">
         <f>INPUT!D117-2</f>
-        <v>2023</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="16">
         <f>INPUT!D117-1</f>
-        <v>2024</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="16" t="str">
         <f>INPUT!D117&amp;" (LTM)"</f>
-        <v>2025 (LTM)</v>
+        <v xml:space="preserve"> (LTM)</v>
       </c>
       <c r="I5" s="16" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="J5" s="16" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="K5" s="16" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="L5" s="16" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="M5" s="16" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5F</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="244"/>
       <c r="B6" s="16" t="s">
         <v>341</v>
@@ -29700,7 +29683,7 @@
       <c r="L6" s="89"/>
       <c r="M6" s="89"/>
     </row>
-    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="245" t="s">
         <v>343</v>
       </c>
@@ -29719,7 +29702,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="246"/>
       <c r="B8" s="16" t="s">
         <v>302</v>
@@ -29745,7 +29728,7 @@
       <c r="M8" s="24"/>
       <c r="N8"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="244"/>
       <c r="B9" s="82" t="s">
         <v>304</v>
@@ -29774,7 +29757,7 @@
       <c r="M9" s="261"/>
       <c r="N9"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="244"/>
       <c r="B10" s="82" t="s">
         <v>201</v>
@@ -29803,7 +29786,7 @@
       <c r="M10" s="261"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="244"/>
       <c r="B11" s="82" t="s">
         <v>96</v>
@@ -29832,7 +29815,7 @@
       <c r="M11" s="261"/>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="244"/>
       <c r="B12" s="82" t="s">
         <v>74</v>
@@ -29861,7 +29844,7 @@
       <c r="M12" s="261"/>
       <c r="N12"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="244"/>
       <c r="B13" s="82" t="s">
         <v>73</v>
@@ -29890,7 +29873,7 @@
       <c r="M13" s="261"/>
       <c r="N13"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="244"/>
       <c r="B14" s="231" t="s">
         <v>460</v>
@@ -29910,7 +29893,7 @@
       <c r="L14" s="89"/>
       <c r="M14" s="89"/>
     </row>
-    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="245" t="s">
         <v>343</v>
       </c>
@@ -29929,7 +29912,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="244"/>
       <c r="B16" s="98" t="s">
         <v>2</v>
@@ -29939,46 +29922,46 @@
       </c>
       <c r="D16" s="236">
         <f>INPUT!D117-4</f>
-        <v>2021</v>
+        <v>-4</v>
       </c>
       <c r="E16" s="236">
         <f>INPUT!D117-3</f>
-        <v>2022</v>
+        <v>-3</v>
       </c>
       <c r="F16" s="236">
         <f>INPUT!D117-2</f>
-        <v>2023</v>
+        <v>-2</v>
       </c>
       <c r="G16" s="236">
         <f>INPUT!D117-1</f>
-        <v>2024</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="236" t="str">
         <f>INPUT!D117&amp;" (LTM)"</f>
-        <v>2025 (LTM)</v>
+        <v xml:space="preserve"> (LTM)</v>
       </c>
       <c r="I16" s="236" t="str">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
-        <v>2026F</v>
+        <v>1F</v>
       </c>
       <c r="J16" s="236" t="str">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
-        <v>2027F</v>
+        <v>2F</v>
       </c>
       <c r="K16" s="236" t="str">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
-        <v>2028F</v>
+        <v>3F</v>
       </c>
       <c r="L16" s="236" t="str">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
-        <v>2029F</v>
+        <v>4F</v>
       </c>
       <c r="M16" s="236" t="str">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
-        <v>2030F</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5F</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="244"/>
       <c r="B17" s="82" t="s">
         <v>5</v>
@@ -30027,7 +30010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="244"/>
       <c r="B18" s="78" t="s">
         <v>7</v>
@@ -30076,7 +30059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="244"/>
       <c r="B19" s="78" t="s">
         <v>18</v>
@@ -30125,7 +30108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="244"/>
       <c r="B20" s="82" t="s">
         <v>16</v>
@@ -30174,7 +30157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="244"/>
       <c r="B21" s="78" t="s">
         <v>305</v>
@@ -30223,7 +30206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="247"/>
       <c r="B22" s="78" t="s">
         <v>96</v>
@@ -30272,7 +30255,7 @@
         <v>–</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="244"/>
       <c r="B23" s="80" t="s">
         <v>314</v>
@@ -30294,10 +30277,10 @@
         <v>–</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="80"/>
     </row>
-    <row r="25" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" ht="21" x14ac:dyDescent="0.5">
       <c r="A25" s="245" t="s">
         <v>343</v>
       </c>
@@ -30316,7 +30299,7 @@
       <c r="L25" s="23"/>
       <c r="M25" s="23"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="244"/>
       <c r="B26" s="98" t="s">
         <v>307</v>
@@ -30340,7 +30323,7 @@
       <c r="M26" s="239"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="244"/>
       <c r="B27" s="82" t="s">
         <v>309</v>
@@ -30369,7 +30352,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="244"/>
       <c r="B28" s="82" t="s">
         <v>310</v>
@@ -30398,7 +30381,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="244"/>
       <c r="B29" s="82" t="s">
         <v>311</v>
@@ -30427,7 +30410,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="244"/>
       <c r="B30" s="82" t="s">
         <v>312</v>
@@ -30456,7 +30439,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="247"/>
       <c r="B31" s="78" t="s">
         <v>313</v>
@@ -30485,7 +30468,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="244"/>
       <c r="B32" s="80" t="s">
         <v>314</v>
@@ -30514,7 +30497,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="245" t="s">
         <v>343</v>
       </c>
@@ -30543,7 +30526,7 @@
       <c r="M33" s="123"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="244"/>
       <c r="B34" s="82" t="s">
         <v>5</v>
@@ -30560,7 +30543,7 @@
       <c r="L34" s="31"/>
       <c r="M34" s="31"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="244"/>
       <c r="B35" s="242" t="str">
         <f>"▶ SCÉNARIO SÉLECTIONNÉ : "&amp;$D$6</f>
@@ -30578,7 +30561,7 @@
       <c r="L35" s="242"/>
       <c r="M35" s="242"/>
     </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="244"/>
       <c r="B36" s="82"/>
       <c r="C36" s="83"/>
@@ -30593,7 +30576,7 @@
       <c r="L36" s="31"/>
       <c r="M36" s="31"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="244"/>
       <c r="B37" s="240" t="s">
         <v>462</v>
@@ -30610,7 +30593,7 @@
       <c r="L37" s="240"/>
       <c r="M37" s="240"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="244"/>
       <c r="B38" s="98" t="s">
         <v>354</v>
@@ -30618,23 +30601,23 @@
       <c r="C38" s="98"/>
       <c r="D38" s="366">
         <f>INPUT!D117+1</f>
-        <v>2026</v>
+        <v>1</v>
       </c>
       <c r="E38" s="366">
         <f>INPUT!D117+2</f>
-        <v>2027</v>
+        <v>2</v>
       </c>
       <c r="F38" s="366">
         <f>INPUT!D117+3</f>
-        <v>2028</v>
+        <v>3</v>
       </c>
       <c r="G38" s="366">
         <f>INPUT!D117+4</f>
-        <v>2029</v>
+        <v>4</v>
       </c>
       <c r="H38" s="366">
         <f>INPUT!D117+5</f>
-        <v>2030</v>
+        <v>5</v>
       </c>
       <c r="I38" s="239"/>
       <c r="J38" s="239"/>
@@ -30642,7 +30625,7 @@
       <c r="L38" s="239"/>
       <c r="M38" s="239"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="244"/>
       <c r="B39" s="82" t="s">
         <v>246</v>
@@ -30674,7 +30657,7 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
     </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="247"/>
       <c r="B40" s="78" t="s">
         <v>303</v>
@@ -30706,7 +30689,7 @@
       <c r="L40" s="31"/>
       <c r="M40" s="31"/>
     </row>
-    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="244"/>
       <c r="B41" s="85" t="s">
         <v>248</v>
@@ -30738,7 +30721,7 @@
       <c r="L41" s="22"/>
       <c r="M41" s="22"/>
     </row>
-    <row r="42" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="245" t="s">
         <v>343</v>
       </c>
@@ -30757,7 +30740,7 @@
       <c r="L42" s="23"/>
       <c r="M42" s="23"/>
     </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="246"/>
       <c r="B43" s="26" t="s">
         <v>463</v>
@@ -30774,7 +30757,7 @@
       <c r="L43" s="26"/>
       <c r="M43" s="26"/>
     </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="244"/>
       <c r="B44" s="16" t="s">
         <v>354</v>
@@ -30782,23 +30765,23 @@
       <c r="C44" s="98"/>
       <c r="D44" s="372">
         <f>INPUT!D117+1</f>
-        <v>2026</v>
+        <v>1</v>
       </c>
       <c r="E44" s="372">
         <f>INPUT!D117+2</f>
-        <v>2027</v>
+        <v>2</v>
       </c>
       <c r="F44" s="372">
         <f>INPUT!D117+3</f>
-        <v>2028</v>
+        <v>3</v>
       </c>
       <c r="G44" s="372">
         <f>INPUT!D117+4</f>
-        <v>2029</v>
+        <v>4</v>
       </c>
       <c r="H44" s="372">
         <f>INPUT!D117+5</f>
-        <v>2030</v>
+        <v>5</v>
       </c>
       <c r="I44" s="241"/>
       <c r="J44" s="241"/>
@@ -30806,7 +30789,7 @@
       <c r="L44" s="241"/>
       <c r="M44" s="241"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="244"/>
       <c r="B45" s="85" t="s">
         <v>246</v>
@@ -30838,7 +30821,7 @@
       <c r="L45" s="31"/>
       <c r="M45" s="31"/>
     </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="244"/>
       <c r="B46" s="85" t="s">
         <v>303</v>
@@ -30870,7 +30853,7 @@
       <c r="L46" s="31"/>
       <c r="M46" s="31"/>
     </row>
-    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="244"/>
       <c r="B47" s="85" t="s">
         <v>248</v>
@@ -30902,7 +30885,7 @@
       <c r="L47" s="31"/>
       <c r="M47" s="31"/>
     </row>
-    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="244"/>
       <c r="B48" s="85" t="s">
         <v>313</v>
@@ -30919,7 +30902,7 @@
       <c r="L48" s="31"/>
       <c r="M48" s="31"/>
     </row>
-    <row r="49" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="247"/>
       <c r="B49" s="80" t="s">
         <v>314</v>
@@ -30936,7 +30919,7 @@
       <c r="L49" s="31"/>
       <c r="M49" s="31"/>
     </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="244"/>
       <c r="B50" s="14"/>
       <c r="C50" s="3"/>
@@ -30951,7 +30934,7 @@
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
     </row>
-    <row r="51" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="244"/>
       <c r="B51" s="44" t="s">
         <v>315</v>
@@ -30968,7 +30951,7 @@
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
     </row>
-    <row r="52" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="244"/>
       <c r="B52" s="14"/>
       <c r="C52" s="3"/>
@@ -30983,7 +30966,7 @@
       <c r="L52" s="22"/>
       <c r="M52" s="22"/>
     </row>
-    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="243"/>
       <c r="B53" s="33" t="s">
         <v>339</v>
@@ -31001,7 +30984,7 @@
       <c r="M53" s="34"/>
       <c r="N53" s="109"/>
     </row>
-    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="243"/>
       <c r="B54" s="33" t="s">
         <v>86</v>
@@ -31019,7 +31002,7 @@
       <c r="M54" s="34"/>
       <c r="N54" s="109"/>
     </row>
-    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="243"/>
       <c r="B55" s="33" t="s">
         <v>340</v>
@@ -31037,7 +31020,7 @@
       <c r="M55" s="34"/>
       <c r="N55" s="109"/>
     </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="244"/>
       <c r="B56" s="14"/>
       <c r="C56" s="3"/>
@@ -31052,14 +31035,14 @@
       <c r="L56" s="22"/>
       <c r="M56" s="22"/>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="246"/>
       <c r="B57" s="16" t="s">
         <v>319</v>
       </c>
       <c r="C57" s="242">
         <f>INPUT!D117+1</f>
-        <v>2026</v>
+        <v>1</v>
       </c>
       <c r="D57" s="94"/>
       <c r="E57" s="94"/>
@@ -31073,7 +31056,7 @@
       <c r="M57" s="24"/>
       <c r="N57" s="111"/>
     </row>
-    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="244"/>
       <c r="B58" s="14" t="s">
         <v>246</v>
@@ -31093,7 +31076,7 @@
       <c r="L58" s="22"/>
       <c r="M58" s="22"/>
     </row>
-    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="244"/>
       <c r="B59" s="14" t="s">
         <v>303</v>
@@ -31113,7 +31096,7 @@
       <c r="L59" s="22"/>
       <c r="M59" s="22"/>
     </row>
-    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="244"/>
       <c r="B60" s="14" t="s">
         <v>248</v>
@@ -31133,7 +31116,7 @@
       <c r="L60" s="22"/>
       <c r="M60" s="22"/>
     </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="244"/>
       <c r="B61" s="14"/>
       <c r="C61" s="3"/>
@@ -31148,7 +31131,7 @@
       <c r="L61" s="22"/>
       <c r="M61" s="22"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="246"/>
       <c r="B62" s="16" t="s">
         <v>320</v>
@@ -31169,7 +31152,7 @@
       <c r="M62" s="24"/>
       <c r="N62" s="111"/>
     </row>
-    <row r="63" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="244"/>
       <c r="B63" s="14" t="s">
         <v>246</v>
@@ -31189,7 +31172,7 @@
       <c r="L63" s="22"/>
       <c r="M63" s="22"/>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="244"/>
       <c r="B64" s="14" t="s">
         <v>303</v>
@@ -31209,7 +31192,7 @@
       <c r="L64" s="22"/>
       <c r="M64" s="22"/>
     </row>
-    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="244"/>
       <c r="B65" s="14" t="s">
         <v>248</v>
@@ -31229,169 +31212,169 @@
       <c r="L65" s="22"/>
       <c r="M65" s="22"/>
     </row>
-    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="51"/>
     </row>
-    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="51"/>
     </row>
-    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="51"/>
     </row>
-    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="51"/>
     </row>
-    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="51"/>
     </row>
-    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
     </row>
-    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
     </row>
-    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="51"/>
     </row>
-    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="51"/>
     </row>
-    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="51"/>
     </row>
-    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="51"/>
     </row>
-    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="51"/>
     </row>
-    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="51"/>
     </row>
-    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="51"/>
     </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="51"/>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="51"/>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="51"/>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="51"/>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="51"/>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="51"/>
     </row>
-    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="51"/>
     </row>
-    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="51"/>
     </row>
-    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="51"/>
     </row>
-    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="51"/>
     </row>
-    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="51"/>
     </row>
-    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="51"/>
     </row>
-    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="51"/>
     </row>
-    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="51"/>
     </row>
-    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="51"/>
     </row>
-    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="51"/>
     </row>
-    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51"/>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
     </row>
-    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
     </row>
-    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
     </row>
-    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
     </row>
-    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
     </row>
-    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
     </row>
-    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
     </row>
-    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
     </row>
-    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
     </row>
-    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
     </row>
-    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
     </row>
-    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
     </row>
-    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
     </row>
-    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
     </row>
-    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
     </row>
-    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
     </row>
-    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
     </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
     </row>
   </sheetData>
@@ -31413,22 +31396,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:XFD120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="12" style="21" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="21" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="21" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" style="21" customWidth="1"/>
-    <col min="10" max="13" width="12.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.85546875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" style="21" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" style="21" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" style="21" customWidth="1"/>
+    <col min="10" max="13" width="12.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.88671875" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="182"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -31447,7 +31430,7 @@
       <c r="N1" s="171"/>
       <c r="O1"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="179"/>
       <c r="B2" s="179"/>
       <c r="C2" s="179"/>
@@ -31464,7 +31447,7 @@
       <c r="N2" s="179"/>
       <c r="O2"/>
     </row>
-    <row r="3" spans="1:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="183" t="s">
         <v>343</v>
       </c>
@@ -31485,7 +31468,7 @@
       <c r="N3" s="181"/>
       <c r="O3"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="179"/>
       <c r="B4" s="179"/>
       <c r="C4" s="179"/>
@@ -31502,7 +31485,7 @@
       <c r="N4" s="179"/>
       <c r="O4"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="179"/>
       <c r="B5" s="179"/>
       <c r="C5" s="179"/>
@@ -31522,7 +31505,7 @@
       <c r="N5" s="179"/>
       <c r="O5"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="179"/>
       <c r="B6" s="179"/>
       <c r="C6" s="179"/>
@@ -31539,7 +31522,7 @@
       <c r="N6" s="179"/>
       <c r="O6"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="179"/>
       <c r="B7" s="179"/>
       <c r="C7" s="179"/>
@@ -31556,7 +31539,7 @@
       <c r="N7" s="179"/>
       <c r="O7"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="179"/>
       <c r="B8" s="170" t="s">
         <v>377</v>
@@ -31577,7 +31560,7 @@
       <c r="N8" s="179"/>
       <c r="O8"/>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="179"/>
       <c r="B9" s="185"/>
       <c r="C9" s="185"/>
@@ -31594,7 +31577,7 @@
       <c r="N9" s="179"/>
       <c r="O9"/>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -31611,7 +31594,7 @@
       <c r="N10" s="179"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="179"/>
       <c r="B11" s="179"/>
       <c r="C11" s="179"/>
@@ -31628,7 +31611,7 @@
       <c r="N11" s="179"/>
       <c r="O11"/>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="179"/>
       <c r="B12" s="179"/>
       <c r="C12" s="179"/>
@@ -31645,7 +31628,7 @@
       <c r="N12" s="179"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="179"/>
       <c r="B13" s="179"/>
       <c r="C13" s="179"/>
@@ -31662,7 +31645,7 @@
       <c r="N13" s="179"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="179"/>
       <c r="B14" s="179"/>
       <c r="C14" s="179"/>
@@ -31679,7 +31662,7 @@
       <c r="N14" s="179"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="179"/>
       <c r="B15" s="179"/>
       <c r="C15" s="179"/>
@@ -31696,7 +31679,7 @@
       <c r="N15" s="179"/>
       <c r="O15"/>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="179"/>
       <c r="B16" s="179"/>
       <c r="C16" s="179"/>
@@ -31713,7 +31696,7 @@
       <c r="N16" s="179"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="179"/>
       <c r="B17" s="179"/>
       <c r="C17" s="179"/>
@@ -31730,7 +31713,7 @@
       <c r="N17" s="179"/>
       <c r="O17"/>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="179"/>
       <c r="B18" s="179"/>
       <c r="C18" s="179"/>
@@ -31747,7 +31730,7 @@
       <c r="N18" s="179"/>
       <c r="O18"/>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="179"/>
       <c r="B19" s="179"/>
       <c r="C19" s="179"/>
@@ -31764,7 +31747,7 @@
       <c r="N19" s="179"/>
       <c r="O19"/>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="179"/>
       <c r="B20" s="179"/>
       <c r="C20" s="179"/>
@@ -31781,7 +31764,7 @@
       <c r="N20" s="179"/>
       <c r="O20"/>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="179"/>
       <c r="B21" s="179"/>
       <c r="C21" s="179"/>
@@ -31798,7 +31781,7 @@
       <c r="N21" s="179"/>
       <c r="O21"/>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="179"/>
       <c r="B22" s="179"/>
       <c r="C22" s="179"/>
@@ -31815,7 +31798,7 @@
       <c r="N22" s="179"/>
       <c r="O22"/>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="179"/>
       <c r="B23" s="179"/>
       <c r="C23" s="179"/>
@@ -31832,7 +31815,7 @@
       <c r="N23" s="179"/>
       <c r="O23"/>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="179"/>
       <c r="B24" s="179"/>
       <c r="C24" s="179"/>
@@ -31849,7 +31832,7 @@
       <c r="N24" s="179"/>
       <c r="O24"/>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="179"/>
       <c r="B25" s="220" t="s">
         <v>438</v>
@@ -31870,7 +31853,7 @@
       <c r="N25" s="179"/>
       <c r="O25"/>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="179"/>
       <c r="B26" s="185"/>
       <c r="C26" s="185"/>
@@ -31887,7 +31870,7 @@
       <c r="N26" s="179"/>
       <c r="O26"/>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="179"/>
       <c r="B27" s="179"/>
       <c r="C27" s="179"/>
@@ -31904,7 +31887,7 @@
       <c r="N27" s="179"/>
       <c r="O27"/>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="179"/>
       <c r="B28" s="179"/>
       <c r="C28" s="179"/>
@@ -31921,7 +31904,7 @@
       <c r="N28" s="179"/>
       <c r="O28"/>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="179"/>
       <c r="B29" s="179"/>
       <c r="C29" s="179"/>
@@ -31938,7 +31921,7 @@
       <c r="N29" s="179"/>
       <c r="O29"/>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="179"/>
       <c r="B30" s="179"/>
       <c r="C30" s="179"/>
@@ -31955,7 +31938,7 @@
       <c r="N30" s="179"/>
       <c r="O30"/>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="179"/>
       <c r="B31" s="179"/>
       <c r="C31" s="179"/>
@@ -31972,7 +31955,7 @@
       <c r="N31" s="179"/>
       <c r="O31"/>
     </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="179"/>
       <c r="B32" s="179"/>
       <c r="C32" s="179"/>
@@ -31989,7 +31972,7 @@
       <c r="N32" s="179"/>
       <c r="O32"/>
     </row>
-    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="179"/>
       <c r="B33" s="179"/>
       <c r="C33" s="179"/>
@@ -32006,7 +31989,7 @@
       <c r="N33" s="179"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="179"/>
       <c r="B34" s="179"/>
       <c r="C34" s="179"/>
@@ -32023,7 +32006,7 @@
       <c r="N34" s="179"/>
       <c r="O34"/>
     </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="179"/>
       <c r="B35" s="179"/>
       <c r="C35" s="179"/>
@@ -32040,7 +32023,7 @@
       <c r="N35" s="179"/>
       <c r="O35"/>
     </row>
-    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="179"/>
       <c r="B36" s="179"/>
       <c r="C36" s="179"/>
@@ -32057,7 +32040,7 @@
       <c r="N36" s="179"/>
       <c r="O36"/>
     </row>
-    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="179"/>
       <c r="B37" s="179"/>
       <c r="C37" s="179"/>
@@ -32074,7 +32057,7 @@
       <c r="N37" s="179"/>
       <c r="O37"/>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="179"/>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -32091,7 +32074,7 @@
       <c r="N38" s="179"/>
       <c r="O38"/>
     </row>
-    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="179"/>
       <c r="B39" s="179"/>
       <c r="C39" s="179"/>
@@ -32108,7 +32091,7 @@
       <c r="N39" s="179"/>
       <c r="O39"/>
     </row>
-    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="179"/>
       <c r="B40" s="179"/>
       <c r="C40" s="179"/>
@@ -32125,7 +32108,7 @@
       <c r="N40" s="179"/>
       <c r="O40"/>
     </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="179"/>
       <c r="B41" s="179"/>
       <c r="C41" s="179"/>
@@ -32142,7 +32125,7 @@
       <c r="N41" s="179"/>
       <c r="O41"/>
     </row>
-    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="179"/>
       <c r="B42" s="218" t="s">
         <v>382</v>
@@ -32162,7 +32145,7 @@
       <c r="N42" s="179"/>
       <c r="O42"/>
     </row>
-    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="179"/>
       <c r="B43" s="179"/>
       <c r="C43" s="179"/>
@@ -32180,7 +32163,7 @@
       <c r="O43" s="179"/>
       <c r="P43" s="179"/>
     </row>
-    <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="179"/>
       <c r="B44" s="179"/>
       <c r="C44" s="195" t="s">
@@ -32206,7 +32189,7 @@
       </c>
       <c r="P44" s="179"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="179"/>
       <c r="B45" s="193" t="s">
         <v>5</v>
@@ -32239,7 +32222,7 @@
       </c>
       <c r="P45" s="179"/>
     </row>
-    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="179"/>
       <c r="B46" s="194"/>
       <c r="C46" s="179"/>
@@ -32253,7 +32236,7 @@
       <c r="L46" s="223"/>
       <c r="P46" s="179"/>
     </row>
-    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="179"/>
       <c r="B47" s="193" t="s">
         <v>359</v>
@@ -32286,7 +32269,7 @@
       </c>
       <c r="P47" s="179"/>
     </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="179"/>
       <c r="B48" s="194"/>
       <c r="C48" s="179"/>
@@ -32300,7 +32283,7 @@
       <c r="L48" s="223"/>
       <c r="P48" s="179"/>
     </row>
-    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="179"/>
       <c r="B49" s="193" t="s">
         <v>360</v>
@@ -32333,7 +32316,7 @@
       </c>
       <c r="P49" s="179"/>
     </row>
-    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="179"/>
       <c r="B50" s="194"/>
       <c r="C50" s="179"/>
@@ -32347,7 +32330,7 @@
       <c r="L50" s="223"/>
       <c r="P50" s="179"/>
     </row>
-    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="179"/>
       <c r="B51" s="193" t="s">
         <v>16</v>
@@ -32380,7 +32363,7 @@
       </c>
       <c r="P51" s="179"/>
     </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="179"/>
       <c r="B52" s="194"/>
       <c r="C52" s="179"/>
@@ -32394,7 +32377,7 @@
       <c r="L52" s="223"/>
       <c r="P52" s="179"/>
     </row>
-    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="179"/>
       <c r="B53" s="193" t="s">
         <v>384</v>
@@ -32427,7 +32410,7 @@
       </c>
       <c r="P53" s="179"/>
     </row>
-    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="179"/>
       <c r="B54" s="179"/>
       <c r="C54" s="179"/>
@@ -32445,7 +32428,7 @@
       <c r="O54" s="179"/>
       <c r="P54" s="179"/>
     </row>
-    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="179"/>
       <c r="B55" s="179"/>
       <c r="C55" s="179"/>
@@ -32463,7 +32446,7 @@
       <c r="O55" s="179"/>
       <c r="P55" s="179"/>
     </row>
-    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="179"/>
       <c r="B56" s="179"/>
       <c r="C56" s="179"/>
@@ -32481,7 +32464,7 @@
       <c r="O56" s="179"/>
       <c r="P56" s="179"/>
     </row>
-    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="179"/>
       <c r="B57" s="179"/>
       <c r="C57" s="179"/>
@@ -32499,7 +32482,7 @@
       <c r="O57" s="179"/>
       <c r="P57" s="179"/>
     </row>
-    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="179"/>
       <c r="B58" s="218" t="s">
         <v>357</v>
@@ -32519,7 +32502,7 @@
       <c r="N58" s="179"/>
       <c r="O58"/>
     </row>
-    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="179"/>
       <c r="B59" s="179"/>
       <c r="C59" s="179"/>
@@ -32536,7 +32519,7 @@
       <c r="N59"/>
       <c r="O59"/>
     </row>
-    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="179"/>
       <c r="B60" s="176" t="s">
         <v>5</v>
@@ -32560,7 +32543,7 @@
       <c r="N60"/>
       <c r="O60"/>
     </row>
-    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="179"/>
       <c r="B61" s="178" t="s">
         <v>359</v>
@@ -32587,7 +32570,7 @@
       <c r="N61"/>
       <c r="O61"/>
     </row>
-    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="179"/>
       <c r="B62" s="179"/>
       <c r="C62" s="179"/>
@@ -32609,7 +32592,7 @@
       <c r="N62"/>
       <c r="O62"/>
     </row>
-    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="179"/>
       <c r="B63" s="176" t="s">
         <v>360</v>
@@ -32631,7 +32614,7 @@
       <c r="N63"/>
       <c r="O63"/>
     </row>
-    <row r="64" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="179"/>
       <c r="B64" s="178" t="s">
         <v>374</v>
@@ -32658,7 +32641,7 @@
       <c r="N64"/>
       <c r="O64"/>
     </row>
-    <row r="65" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="179"/>
       <c r="B65" s="178" t="s">
         <v>375</v>
@@ -32680,7 +32663,7 @@
       <c r="N65"/>
       <c r="O65"/>
     </row>
-    <row r="66" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="179"/>
       <c r="B66" s="178" t="s">
         <v>376</v>
@@ -32707,7 +32690,7 @@
       <c r="N66"/>
       <c r="O66"/>
     </row>
-    <row r="67" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="179"/>
       <c r="B67" s="178" t="s">
         <v>361</v>
@@ -32734,7 +32717,7 @@
       <c r="N67"/>
       <c r="O67"/>
     </row>
-    <row r="68" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="179"/>
       <c r="B68" s="178" t="s">
         <v>371</v>
@@ -32761,7 +32744,7 @@
       <c r="N68"/>
       <c r="O68"/>
     </row>
-    <row r="69" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="179"/>
       <c r="B69" s="179"/>
       <c r="C69" s="179"/>
@@ -32783,7 +32766,7 @@
       <c r="N69"/>
       <c r="O69"/>
     </row>
-    <row r="70" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="179"/>
       <c r="B70" s="179"/>
       <c r="C70" s="179"/>
@@ -32806,7 +32789,7 @@
       <c r="N70"/>
       <c r="O70"/>
     </row>
-    <row r="71" spans="1:15 16369:16369" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15 16369:16369" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="179"/>
       <c r="B71" s="176" t="s">
         <v>373</v>
@@ -32833,7 +32816,7 @@
       <c r="N71"/>
       <c r="O71"/>
     </row>
-    <row r="72" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="179"/>
       <c r="B72" s="179"/>
       <c r="C72" s="179"/>
@@ -32850,13 +32833,13 @@
       <c r="N72"/>
       <c r="O72"/>
     </row>
-    <row r="73" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L73" s="179"/>
       <c r="M73"/>
       <c r="N73"/>
       <c r="O73"/>
     </row>
-    <row r="74" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K74" s="179"/>
       <c r="L74"/>
       <c r="M74"/>
@@ -32864,7 +32847,7 @@
       <c r="O74"/>
       <c r="XEO74" s="179"/>
     </row>
-    <row r="75" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K75" s="179"/>
       <c r="L75"/>
       <c r="M75"/>
@@ -32872,13 +32855,13 @@
       <c r="O75"/>
       <c r="XEO75" s="179"/>
     </row>
-    <row r="76" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O76"/>
     </row>
-    <row r="77" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O77"/>
     </row>
-    <row r="78" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="232"/>
       <c r="B78" s="408"/>
       <c r="C78" s="408"/>
@@ -32895,7 +32878,7 @@
       <c r="N78" s="233"/>
       <c r="O78" s="233"/>
     </row>
-    <row r="79" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="232"/>
       <c r="B79" s="408"/>
       <c r="C79" s="408"/>
@@ -32912,7 +32895,7 @@
       <c r="N79" s="233"/>
       <c r="O79" s="233"/>
     </row>
-    <row r="80" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15 16369:16369" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="232"/>
       <c r="B80" s="408"/>
       <c r="C80" s="408"/>
@@ -32929,7 +32912,7 @@
       <c r="N80" s="233"/>
       <c r="O80" s="233"/>
     </row>
-    <row r="81" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="233"/>
       <c r="B81" s="233"/>
       <c r="C81" s="409" t="str">
@@ -32976,7 +32959,7 @@
       <c r="N81" s="412"/>
       <c r="O81" s="233"/>
     </row>
-    <row r="82" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="233"/>
       <c r="B82" s="233" t="s">
         <v>5</v>
@@ -33010,7 +32993,7 @@
       <c r="N82" s="412"/>
       <c r="O82" s="233"/>
     </row>
-    <row r="83" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="233"/>
       <c r="B83" s="233"/>
       <c r="C83" s="233" t="s">
@@ -33044,7 +33027,7 @@
       <c r="N83" s="412"/>
       <c r="O83" s="412"/>
     </row>
-    <row r="84" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="233"/>
       <c r="B84" s="233"/>
       <c r="C84" s="233" t="s">
@@ -33078,7 +33061,7 @@
       <c r="N84" s="412"/>
       <c r="O84" s="412"/>
     </row>
-    <row r="85" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="233"/>
       <c r="B85" s="233"/>
       <c r="C85" s="233"/>
@@ -33110,7 +33093,7 @@
       </c>
       <c r="O85" s="412"/>
     </row>
-    <row r="86" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="233"/>
       <c r="B86" s="233"/>
       <c r="C86" s="233"/>
@@ -33144,7 +33127,7 @@
       </c>
       <c r="O86" s="412"/>
     </row>
-    <row r="87" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="233"/>
       <c r="B87" s="233"/>
       <c r="C87" s="233"/>
@@ -33178,7 +33161,7 @@
       </c>
       <c r="O87" s="412"/>
     </row>
-    <row r="88" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="233"/>
       <c r="B88" s="233"/>
       <c r="C88" s="233"/>
@@ -33227,7 +33210,7 @@
       </c>
       <c r="O88" s="412"/>
     </row>
-    <row r="89" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="233"/>
       <c r="B89" s="233"/>
       <c r="C89" s="233" t="s">
@@ -33261,7 +33244,7 @@
       <c r="N89" s="412"/>
       <c r="O89" s="412"/>
     </row>
-    <row r="90" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="233"/>
       <c r="B90" s="233"/>
       <c r="C90" s="233"/>
@@ -33293,7 +33276,7 @@
       </c>
       <c r="O90" s="412"/>
     </row>
-    <row r="91" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="233"/>
       <c r="B91" s="233"/>
       <c r="C91" s="233"/>
@@ -33338,7 +33321,7 @@
       <c r="XFC91" s="21"/>
       <c r="XFD91" s="21"/>
     </row>
-    <row r="92" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="233"/>
       <c r="B92" s="233"/>
       <c r="C92" s="233"/>
@@ -33383,7 +33366,7 @@
       <c r="XFC92" s="21"/>
       <c r="XFD92" s="21"/>
     </row>
-    <row r="93" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="233"/>
       <c r="B93" s="233"/>
       <c r="C93" s="233"/>
@@ -33417,7 +33400,7 @@
       </c>
       <c r="O93" s="412"/>
     </row>
-    <row r="94" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="233"/>
       <c r="B94" s="233"/>
       <c r="C94" s="233"/>
@@ -33451,7 +33434,7 @@
       </c>
       <c r="O94" s="412"/>
     </row>
-    <row r="95" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="233"/>
       <c r="B95" s="233"/>
       <c r="C95" s="233"/>
@@ -33468,79 +33451,79 @@
       <c r="N95" s="412"/>
       <c r="O95" s="412"/>
     </row>
-    <row r="96" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15 16373:16384" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="51"/>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="51"/>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="51"/>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="51"/>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="51"/>
     </row>
-    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="51"/>
     </row>
-    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="51"/>
     </row>
-    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="51"/>
     </row>
-    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="51"/>
     </row>
-    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="51"/>
     </row>
-    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="51"/>
     </row>
-    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="51"/>
     </row>
-    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="51"/>
     </row>
-    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="51"/>
     </row>
-    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="51"/>
     </row>
-    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="51"/>
     </row>
-    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="51"/>
     </row>
-    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="51"/>
     </row>
-    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="51"/>
     </row>
-    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="51"/>
     </row>
-    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="51"/>
     </row>
-    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="51"/>
     </row>
-    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="51"/>
     </row>
-    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="51"/>
     </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="51"/>
     </row>
   </sheetData>
@@ -33558,28 +33541,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AFD438-635F-454C-BFF5-509400E21BDF}">
   <dimension ref="A1:AF107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="167" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="167" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" style="167" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="167" customWidth="1"/>
-    <col min="6" max="10" width="12.42578125" style="167" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="167" customWidth="1"/>
-    <col min="12" max="14" width="12.42578125" style="167" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="168" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="167" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" style="167" customWidth="1"/>
-    <col min="18" max="18" width="16.7109375" style="167" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" style="167" customWidth="1"/>
-    <col min="20" max="20" width="26.140625" style="167" customWidth="1"/>
-    <col min="21" max="21" width="18.28515625" style="167" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="167" customWidth="1"/>
-    <col min="23" max="30" width="12.42578125" style="167" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="167"/>
+    <col min="1" max="1" width="15.33203125" style="167" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="167" customWidth="1"/>
+    <col min="3" max="4" width="12.44140625" style="167" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="167" customWidth="1"/>
+    <col min="6" max="10" width="12.44140625" style="167" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" style="167" customWidth="1"/>
+    <col min="12" max="14" width="12.44140625" style="167" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="168" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="167" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" style="167" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" style="167" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="167" customWidth="1"/>
+    <col min="20" max="20" width="26.109375" style="167" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="167" customWidth="1"/>
+    <col min="22" max="22" width="16.109375" style="167" customWidth="1"/>
+    <col min="23" max="30" width="12.44140625" style="167" customWidth="1"/>
+    <col min="31" max="16384" width="9.109375" style="167"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="182"/>
       <c r="B1" s="118" t="s">
         <v>346</v>
@@ -33616,7 +33599,7 @@
       <c r="AC1" s="217"/>
       <c r="AD1" s="217"/>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="102"/>
       <c r="B2" s="102"/>
       <c r="C2" s="102"/>
@@ -33648,7 +33631,7 @@
       <c r="AC2"/>
       <c r="AD2"/>
     </row>
-    <row r="3" spans="1:30" s="169" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" s="169" customFormat="1" ht="21" x14ac:dyDescent="0.5">
       <c r="A3"/>
       <c r="B3" s="155" t="s">
         <v>385</v>
@@ -33684,7 +33667,7 @@
       <c r="AC3"/>
       <c r="AD3"/>
     </row>
-    <row r="4" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="102"/>
       <c r="B4" s="102"/>
       <c r="C4" s="102"/>
@@ -33750,7 +33733,7 @@
       <c r="AC5"/>
       <c r="AD5"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="102"/>
       <c r="B6" s="390" t="str">
         <f>CONCATENATE("Company: ",INPUT!D114)</f>
@@ -33790,7 +33773,7 @@
       <c r="AC6"/>
       <c r="AD6"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="102"/>
       <c r="B7" s="102"/>
       <c r="C7" s="102"/>
@@ -33827,7 +33810,7 @@
       <c r="AC7"/>
       <c r="AD7"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="102"/>
       <c r="B8" s="102"/>
       <c r="C8" s="102"/>
@@ -33864,7 +33847,7 @@
       <c r="AC8"/>
       <c r="AD8"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="102"/>
       <c r="B9" s="102"/>
       <c r="C9" s="102"/>
@@ -33901,7 +33884,7 @@
       <c r="AC9"/>
       <c r="AD9"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="102"/>
       <c r="B10" s="102"/>
       <c r="C10" s="102"/>
@@ -33924,7 +33907,7 @@
       </c>
       <c r="S10" s="392">
         <f>INPUT!D117</f>
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="T10"/>
       <c r="U10"/>
@@ -33938,7 +33921,7 @@
       <c r="AC10"/>
       <c r="AD10"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="102"/>
       <c r="B11" s="102"/>
       <c r="C11" s="102"/>
@@ -33975,7 +33958,7 @@
       <c r="AC11"/>
       <c r="AD11"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="102"/>
       <c r="B12" s="102"/>
       <c r="C12" s="102"/>
@@ -34012,7 +33995,7 @@
       <c r="AC12"/>
       <c r="AD12"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="102"/>
       <c r="B13" s="102"/>
       <c r="C13" s="102"/>
@@ -34044,7 +34027,7 @@
       <c r="AC13"/>
       <c r="AD13"/>
     </row>
-    <row r="14" spans="1:30" ht="21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="21" x14ac:dyDescent="0.5">
       <c r="A14" s="102"/>
       <c r="B14" s="102"/>
       <c r="C14" s="102"/>
@@ -34078,7 +34061,7 @@
       <c r="AC14"/>
       <c r="AD14"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="102"/>
       <c r="B15" s="102"/>
       <c r="C15" s="102"/>
@@ -34110,7 +34093,7 @@
       <c r="AC15"/>
       <c r="AD15"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="102"/>
       <c r="B16" s="102"/>
       <c r="C16" s="102"/>
@@ -34148,7 +34131,7 @@
       <c r="AC16"/>
       <c r="AD16"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="102"/>
       <c r="B17" s="102"/>
       <c r="C17" s="102"/>
@@ -34191,7 +34174,7 @@
       <c r="AC17"/>
       <c r="AD17"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="102"/>
       <c r="B18" s="102"/>
       <c r="C18" s="102"/>
@@ -34234,7 +34217,7 @@
       <c r="AC18"/>
       <c r="AD18"/>
     </row>
-    <row r="19" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="102"/>
       <c r="B19" s="220" t="s">
         <v>391</v>
@@ -34281,7 +34264,7 @@
       <c r="AC19"/>
       <c r="AD19"/>
     </row>
-    <row r="20" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="102"/>
       <c r="B20" s="190"/>
       <c r="C20" s="102"/>
@@ -34324,7 +34307,7 @@
       <c r="AC20"/>
       <c r="AD20"/>
     </row>
-    <row r="21" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="102"/>
       <c r="B21" s="102"/>
       <c r="C21" s="102"/>
@@ -34367,7 +34350,7 @@
       <c r="AC21"/>
       <c r="AD21"/>
     </row>
-    <row r="22" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="102"/>
       <c r="B22" s="102"/>
       <c r="C22" s="102"/>
@@ -34404,7 +34387,7 @@
       <c r="AC22"/>
       <c r="AD22"/>
     </row>
-    <row r="23" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="102"/>
       <c r="B23" s="102"/>
       <c r="C23" s="102"/>
@@ -34436,7 +34419,7 @@
       <c r="AC23"/>
       <c r="AD23"/>
     </row>
-    <row r="24" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="102"/>
       <c r="B24" s="102"/>
       <c r="C24" s="102"/>
@@ -34468,7 +34451,7 @@
       <c r="AC24"/>
       <c r="AD24"/>
     </row>
-    <row r="25" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="102"/>
       <c r="B25" s="102"/>
       <c r="C25" s="102"/>
@@ -34500,7 +34483,7 @@
       <c r="AC25"/>
       <c r="AD25"/>
     </row>
-    <row r="26" spans="1:30" s="169" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" s="169" customFormat="1" ht="21" x14ac:dyDescent="0.5">
       <c r="A26" s="102"/>
       <c r="B26" s="102"/>
       <c r="C26" s="102"/>
@@ -34534,7 +34517,7 @@
       <c r="AC26"/>
       <c r="AD26"/>
     </row>
-    <row r="27" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" s="169" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="102"/>
       <c r="B27" s="102"/>
       <c r="C27" s="102"/>
@@ -34566,7 +34549,7 @@
       <c r="AC27"/>
       <c r="AD27"/>
     </row>
-    <row r="28" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="102"/>
       <c r="B28" s="102"/>
       <c r="C28" s="102"/>
@@ -34615,7 +34598,7 @@
       <c r="AC28"/>
       <c r="AD28"/>
     </row>
-    <row r="29" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="102"/>
       <c r="B29" s="102"/>
       <c r="C29" s="102"/>
@@ -34647,7 +34630,7 @@
       <c r="AC29"/>
       <c r="AD29"/>
     </row>
-    <row r="30" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="102"/>
       <c r="B30" s="102"/>
       <c r="C30" s="102"/>
@@ -34696,7 +34679,7 @@
       <c r="AC30"/>
       <c r="AD30"/>
     </row>
-    <row r="31" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="102"/>
       <c r="B31" s="102"/>
       <c r="C31" s="102"/>
@@ -34739,7 +34722,7 @@
       <c r="AC31"/>
       <c r="AD31"/>
     </row>
-    <row r="32" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="102"/>
       <c r="B32" s="102"/>
       <c r="C32" s="102"/>
@@ -34771,7 +34754,7 @@
       <c r="AC32"/>
       <c r="AD32"/>
     </row>
-    <row r="33" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="102"/>
       <c r="B33" s="102"/>
       <c r="C33" s="102"/>
@@ -34805,7 +34788,7 @@
       <c r="AC33"/>
       <c r="AD33"/>
     </row>
-    <row r="34" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="102"/>
       <c r="B34" s="102"/>
       <c r="C34" s="102"/>
@@ -34854,7 +34837,7 @@
       <c r="AC34"/>
       <c r="AD34"/>
     </row>
-    <row r="35" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="102"/>
       <c r="B35" s="102"/>
       <c r="C35" s="102"/>
@@ -34903,7 +34886,7 @@
       <c r="AC35"/>
       <c r="AD35"/>
     </row>
-    <row r="36" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="102"/>
       <c r="B36" s="102"/>
       <c r="C36" s="102"/>
@@ -34952,7 +34935,7 @@
       <c r="AC36"/>
       <c r="AD36"/>
     </row>
-    <row r="37" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="102"/>
       <c r="B37" s="102"/>
       <c r="C37" s="102"/>
@@ -35001,7 +34984,7 @@
       <c r="AC37"/>
       <c r="AD37"/>
     </row>
-    <row r="38" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="102"/>
       <c r="B38" s="102"/>
       <c r="C38" s="102"/>
@@ -35050,7 +35033,7 @@
       <c r="AC38"/>
       <c r="AD38"/>
     </row>
-    <row r="39" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39"/>
       <c r="B39" s="220" t="s">
         <v>404</v>
@@ -35086,7 +35069,7 @@
       <c r="AC39"/>
       <c r="AD39"/>
     </row>
-    <row r="40" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -35135,7 +35118,7 @@
       <c r="AC40"/>
       <c r="AD40"/>
     </row>
-    <row r="41" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -35184,7 +35167,7 @@
       <c r="AC41"/>
       <c r="AD41"/>
     </row>
-    <row r="42" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -35233,7 +35216,7 @@
       <c r="AC42"/>
       <c r="AD42"/>
     </row>
-    <row r="43" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -35265,7 +35248,7 @@
       <c r="AC43"/>
       <c r="AD43"/>
     </row>
-    <row r="44" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -35294,7 +35277,7 @@
       <c r="Z44"/>
       <c r="AA44"/>
     </row>
-    <row r="45" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
@@ -35326,7 +35309,7 @@
       <c r="AC45"/>
       <c r="AD45"/>
     </row>
-    <row r="46" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -35358,7 +35341,7 @@
       <c r="AC46"/>
       <c r="AD46"/>
     </row>
-    <row r="47" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -35390,7 +35373,7 @@
       <c r="AC47"/>
       <c r="AD47"/>
     </row>
-    <row r="48" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -35422,7 +35405,7 @@
       <c r="AC48"/>
       <c r="AD48"/>
     </row>
-    <row r="49" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -35454,7 +35437,7 @@
       <c r="AC49"/>
       <c r="AD49"/>
     </row>
-    <row r="50" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
@@ -35486,7 +35469,7 @@
       <c r="AC50"/>
       <c r="AD50"/>
     </row>
-    <row r="51" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
@@ -35518,7 +35501,7 @@
       <c r="AC51"/>
       <c r="AD51"/>
     </row>
-    <row r="52" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
@@ -35550,7 +35533,7 @@
       <c r="AC52"/>
       <c r="AD52"/>
     </row>
-    <row r="53" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
@@ -35582,7 +35565,7 @@
       <c r="AC53"/>
       <c r="AD53"/>
     </row>
-    <row r="54" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
@@ -35614,7 +35597,7 @@
       <c r="AC54"/>
       <c r="AD54"/>
     </row>
-    <row r="55" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -35646,7 +35629,7 @@
       <c r="AC55"/>
       <c r="AD55"/>
     </row>
-    <row r="56" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -35679,7 +35662,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -35712,7 +35695,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
@@ -35745,7 +35728,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
@@ -35778,7 +35761,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -35812,7 +35795,7 @@
       <c r="AE60"/>
       <c r="AF60"/>
     </row>
-    <row r="61" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:32" s="166" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -35846,7 +35829,7 @@
       <c r="AE61"/>
       <c r="AF61"/>
     </row>
-    <row r="62" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
@@ -35880,7 +35863,7 @@
       <c r="AE62"/>
       <c r="AF62"/>
     </row>
-    <row r="63" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
@@ -35914,7 +35897,7 @@
       <c r="AE63"/>
       <c r="AF63"/>
     </row>
-    <row r="64" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -35948,7 +35931,7 @@
       <c r="AE64"/>
       <c r="AF64"/>
     </row>
-    <row r="65" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
@@ -35982,7 +35965,7 @@
       <c r="AE65"/>
       <c r="AF65"/>
     </row>
-    <row r="66" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
@@ -36016,7 +35999,7 @@
       <c r="AE66"/>
       <c r="AF66"/>
     </row>
-    <row r="67" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67"/>
       <c r="C67" s="201"/>
       <c r="D67" s="201"/>
@@ -36042,7 +36025,7 @@
       <c r="AE67"/>
       <c r="AF67"/>
     </row>
-    <row r="68" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68"/>
       <c r="B68" s="169"/>
       <c r="C68" s="202"/>
@@ -36076,7 +36059,7 @@
       <c r="AE68"/>
       <c r="AF68"/>
     </row>
-    <row r="69" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69"/>
       <c r="B69" s="169"/>
       <c r="C69" s="201"/>
@@ -36109,7 +36092,7 @@
       <c r="AE69"/>
       <c r="AF69"/>
     </row>
-    <row r="70" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70"/>
       <c r="B70" s="169"/>
       <c r="C70" s="201"/>
@@ -36143,7 +36126,7 @@
       <c r="AE70"/>
       <c r="AF70"/>
     </row>
-    <row r="71" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71"/>
       <c r="B71" s="169"/>
       <c r="C71" s="201"/>
@@ -36177,7 +36160,7 @@
       <c r="AE71"/>
       <c r="AF71"/>
     </row>
-    <row r="72" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72"/>
       <c r="B72" s="166"/>
       <c r="C72" s="201"/>
@@ -36211,7 +36194,7 @@
       <c r="AE72"/>
       <c r="AF72"/>
     </row>
-    <row r="73" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73"/>
       <c r="B73" s="169"/>
       <c r="C73" s="201"/>
@@ -36245,7 +36228,7 @@
       <c r="AE73"/>
       <c r="AF73"/>
     </row>
-    <row r="74" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74"/>
       <c r="B74" s="169"/>
       <c r="C74" s="201"/>
@@ -36279,7 +36262,7 @@
       <c r="AE74"/>
       <c r="AF74"/>
     </row>
-    <row r="75" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75"/>
       <c r="B75" s="169"/>
       <c r="C75" s="201"/>
@@ -36313,7 +36296,7 @@
       <c r="AE75"/>
       <c r="AF75"/>
     </row>
-    <row r="76" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B76" s="169"/>
       <c r="C76" s="201"/>
       <c r="D76" s="201"/>
@@ -36333,7 +36316,7 @@
       <c r="R76" s="169"/>
       <c r="S76" s="169"/>
     </row>
-    <row r="77" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B77" s="166"/>
       <c r="C77" s="201"/>
       <c r="D77" s="201"/>
@@ -36353,7 +36336,7 @@
       <c r="R77" s="166"/>
       <c r="S77" s="166"/>
     </row>
-    <row r="78" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="166"/>
       <c r="C78" s="201"/>
       <c r="D78" s="201"/>
@@ -36373,7 +36356,7 @@
       <c r="R78" s="166"/>
       <c r="S78" s="166"/>
     </row>
-    <row r="79" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B79" s="166"/>
       <c r="C79" s="201"/>
       <c r="D79" s="201"/>
@@ -36393,7 +36376,7 @@
       <c r="R79" s="166"/>
       <c r="S79" s="166"/>
     </row>
-    <row r="80" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B80" s="166"/>
       <c r="C80" s="201"/>
       <c r="D80" s="201"/>
@@ -36413,7 +36396,7 @@
       <c r="R80" s="166"/>
       <c r="S80" s="166"/>
     </row>
-    <row r="81" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B81" s="166"/>
       <c r="C81" s="201"/>
       <c r="D81" s="201"/>
@@ -36433,7 +36416,7 @@
       <c r="R81" s="166"/>
       <c r="S81" s="166"/>
     </row>
-    <row r="82" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B82" s="166"/>
       <c r="C82" s="201"/>
       <c r="D82" s="201"/>
@@ -36453,7 +36436,7 @@
       <c r="R82" s="166"/>
       <c r="S82" s="166"/>
     </row>
-    <row r="83" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B83" s="166"/>
       <c r="C83" s="201"/>
       <c r="D83" s="201"/>
@@ -36473,7 +36456,7 @@
       <c r="R83" s="166"/>
       <c r="S83" s="166"/>
     </row>
-    <row r="84" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B84" s="166"/>
       <c r="C84" s="201"/>
       <c r="D84" s="201"/>
@@ -36493,7 +36476,7 @@
       <c r="R84" s="166"/>
       <c r="S84" s="166"/>
     </row>
-    <row r="85" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B85" s="166"/>
       <c r="C85" s="201"/>
       <c r="D85" s="201"/>
@@ -36513,7 +36496,7 @@
       <c r="R85" s="166"/>
       <c r="S85" s="166"/>
     </row>
-    <row r="86" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="166"/>
       <c r="C86" s="166"/>
       <c r="D86" s="166"/>
@@ -36533,7 +36516,7 @@
       <c r="R86" s="166"/>
       <c r="S86" s="166"/>
     </row>
-    <row r="87" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B87" s="166"/>
       <c r="C87" s="201"/>
       <c r="D87" s="201"/>
@@ -36553,7 +36536,7 @@
       <c r="R87" s="209"/>
       <c r="S87" s="166"/>
     </row>
-    <row r="88" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B88" s="166"/>
       <c r="C88" s="210"/>
       <c r="D88" s="211"/>
@@ -36573,7 +36556,7 @@
       <c r="R88" s="212"/>
       <c r="S88" s="166"/>
     </row>
-    <row r="89" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="213"/>
       <c r="B89" s="213"/>
       <c r="C89" s="214"/>
@@ -36604,7 +36587,7 @@
       <c r="AB89" s="213"/>
       <c r="AC89" s="213"/>
     </row>
-    <row r="90" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="213"/>
       <c r="B90" s="213"/>
       <c r="C90" s="213"/>
@@ -36635,7 +36618,7 @@
       <c r="AB90" s="213"/>
       <c r="AC90" s="213"/>
     </row>
-    <row r="91" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="213"/>
       <c r="B91" s="213"/>
       <c r="C91" s="213"/>
@@ -36666,7 +36649,7 @@
       <c r="AB91" s="213"/>
       <c r="AC91" s="213"/>
     </row>
-    <row r="92" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="213"/>
       <c r="B92" s="213"/>
       <c r="C92" s="213"/>
@@ -36697,7 +36680,7 @@
       <c r="AB92" s="213"/>
       <c r="AC92" s="213"/>
     </row>
-    <row r="93" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="213"/>
       <c r="B93" s="213"/>
       <c r="C93" s="213"/>
@@ -36728,7 +36711,7 @@
       <c r="AB93" s="213"/>
       <c r="AC93" s="213"/>
     </row>
-    <row r="94" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="213"/>
       <c r="B94" s="213"/>
       <c r="C94" s="213"/>
@@ -36759,7 +36742,7 @@
       <c r="AB94" s="213"/>
       <c r="AC94" s="213"/>
     </row>
-    <row r="95" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="213"/>
       <c r="B95" s="213"/>
       <c r="C95" s="213"/>
@@ -36796,7 +36779,7 @@
       <c r="AB95" s="213"/>
       <c r="AC95" s="213"/>
     </row>
-    <row r="96" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="213"/>
       <c r="B96" s="213"/>
       <c r="C96" s="213"/>
@@ -36838,7 +36821,7 @@
       <c r="AB96" s="213"/>
       <c r="AC96" s="213"/>
     </row>
-    <row r="97" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="213"/>
       <c r="B97" s="213"/>
       <c r="C97" s="213"/>
@@ -36880,7 +36863,7 @@
       <c r="AB97" s="213"/>
       <c r="AC97" s="213"/>
     </row>
-    <row r="98" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="213"/>
       <c r="B98" s="213"/>
       <c r="C98" s="213"/>
@@ -36922,7 +36905,7 @@
       <c r="AB98" s="213"/>
       <c r="AC98" s="213"/>
     </row>
-    <row r="99" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="213"/>
       <c r="B99" s="213"/>
       <c r="C99" s="213"/>
@@ -36964,7 +36947,7 @@
       <c r="AB99" s="213"/>
       <c r="AC99" s="213"/>
     </row>
-    <row r="100" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="213"/>
       <c r="B100" s="213"/>
       <c r="C100" s="213"/>
@@ -37006,7 +36989,7 @@
       <c r="AB100" s="213"/>
       <c r="AC100" s="213"/>
     </row>
-    <row r="101" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="213"/>
       <c r="B101" s="213"/>
       <c r="C101" s="213"/>
@@ -37037,7 +37020,7 @@
       <c r="AB101" s="213"/>
       <c r="AC101" s="213"/>
     </row>
-    <row r="102" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="213"/>
       <c r="B102" s="213"/>
       <c r="C102" s="213"/>
@@ -37068,7 +37051,7 @@
       <c r="AB102" s="213"/>
       <c r="AC102" s="213"/>
     </row>
-    <row r="103" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="213"/>
       <c r="B103" s="213" t="s">
         <v>354</v>
@@ -37148,7 +37131,7 @@
       <c r="AB103" s="213"/>
       <c r="AC103" s="213"/>
     </row>
-    <row r="104" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="213"/>
       <c r="B104" s="213" t="s">
         <v>395</v>
@@ -37228,7 +37211,7 @@
       <c r="AB104" s="213"/>
       <c r="AC104" s="213"/>
     </row>
-    <row r="105" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="213"/>
       <c r="B105" s="213" t="s">
         <v>404</v>
@@ -37308,7 +37291,7 @@
       <c r="AB105" s="213"/>
       <c r="AC105" s="213"/>
     </row>
-    <row r="106" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="213" t="s">
         <v>5</v>
       </c>
@@ -37373,7 +37356,7 @@
       <c r="AB106" s="213"/>
       <c r="AC106" s="213"/>
     </row>
-    <row r="107" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B107" s="166"/>
       <c r="C107" s="166"/>
       <c r="D107" s="166"/>

--- a/assets/TEMPLATE.xlsx
+++ b/assets/TEMPLATE.xlsx
@@ -11514,23 +11514,23 @@
       </c>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="1">
-        <f>INPUT!D5</f>
+        <f>IF(INPUT!D5="","",INPUT!D5)</f>
         <v/>
       </c>
       <c r="E5" s="1">
-        <f>INPUT!E5</f>
+        <f>IF(INPUT!E5="","",INPUT!E5)</f>
         <v/>
       </c>
       <c r="F5" s="1">
-        <f>INPUT!F5</f>
+        <f>IF(INPUT!F5="","",INPUT!F5)</f>
         <v/>
       </c>
       <c r="G5" s="1">
-        <f>INPUT!G5</f>
+        <f>IF(INPUT!G5="","",INPUT!G5)</f>
         <v/>
       </c>
       <c r="H5" s="1">
-        <f>INPUT!H5</f>
+        <f>IF(INPUT!H5="","",INPUT!H5)</f>
         <v/>
       </c>
     </row>
@@ -13778,23 +13778,23 @@
       </c>
       <c r="C5" s="138" t="n"/>
       <c r="D5" s="138">
-        <f>INPUT!D5</f>
+        <f>IF(INPUT!D5="","",INPUT!D5)</f>
         <v/>
       </c>
       <c r="E5" s="138">
-        <f>INPUT!E5</f>
+        <f>IF(INPUT!E5="","",INPUT!E5)</f>
         <v/>
       </c>
       <c r="F5" s="138">
-        <f>INPUT!F5</f>
+        <f>IF(INPUT!F5="","",INPUT!F5)</f>
         <v/>
       </c>
       <c r="G5" s="138">
-        <f>INPUT!G5</f>
+        <f>IF(INPUT!G5="","",INPUT!G5)</f>
         <v/>
       </c>
       <c r="H5" s="138">
-        <f>INPUT!H5</f>
+        <f>IF(INPUT!H5="","",INPUT!H5)</f>
         <v/>
       </c>
       <c r="I5" s="24" t="n"/>
@@ -15026,7 +15026,7 @@
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>INPUT!H5</f>
+        <f>IF(INPUT!H5="","",INPUT!H5)</f>
         <v/>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -16258,23 +16258,23 @@
         </is>
       </c>
       <c r="D5" s="24">
-        <f>INPUT!D5</f>
+        <f>IF(INPUT!D5="","",INPUT!D5)</f>
         <v/>
       </c>
       <c r="E5" s="24">
-        <f>INPUT!E5</f>
+        <f>IF(INPUT!E5="","",INPUT!E5)</f>
         <v/>
       </c>
       <c r="F5" s="24">
-        <f>INPUT!F5</f>
+        <f>IF(INPUT!F5="","",INPUT!F5)</f>
         <v/>
       </c>
       <c r="G5" s="24">
-        <f>INPUT!G5</f>
+        <f>IF(INPUT!G5="","",INPUT!G5)</f>
         <v/>
       </c>
       <c r="H5" s="24">
-        <f>INPUT!H5</f>
+        <f>IF(INPUT!H5="","",INPUT!H5)</f>
         <v/>
       </c>
       <c r="I5" s="24">

--- a/assets/TEMPLATE.xlsx
+++ b/assets/TEMPLATE.xlsx
@@ -3532,7 +3532,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>ACME Share Price</v>
+            <strRef>
+              <f>INPUT!$D$115</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Share Price</v>
+                </pt>
+              </strCache>
+            </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
@@ -13442,7 +13450,28 @@
     <row r="89" ht="15" customHeight="1">
       <c r="B89" s="51" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1"/>
+    <row r="90" ht="15" customHeight="1">
+      <c r="D90" s="22">
+        <f>IF(INPUT!D9="",NA(),D5)</f>
+        <v/>
+      </c>
+      <c r="E90" s="22">
+        <f>IF(INPUT!E9="",NA(),E5)</f>
+        <v/>
+      </c>
+      <c r="F90" s="22">
+        <f>IF(INPUT!F9="",NA(),F5)</f>
+        <v/>
+      </c>
+      <c r="G90" s="22">
+        <f>IF(INPUT!G9="",NA(),G5)</f>
+        <v/>
+      </c>
+      <c r="H90" s="22">
+        <f>IF(INPUT!H9="",NA(),H5)</f>
+        <v/>
+      </c>
+    </row>
     <row r="91" ht="15" customHeight="1">
       <c r="B91" s="51" t="inlineStr">
         <is>
@@ -13489,11 +13518,11 @@
         <v/>
       </c>
       <c r="G92" s="433">
-        <f>G85/1000</f>
+        <f>G86/1000</f>
         <v/>
       </c>
       <c r="H92" s="433">
-        <f>H85/1000</f>
+        <f>H86/1000</f>
         <v/>
       </c>
     </row>
@@ -13516,11 +13545,11 @@
         <v/>
       </c>
       <c r="G93" s="433">
-        <f>G86/1000</f>
+        <f>G87/1000</f>
         <v/>
       </c>
       <c r="H93" s="433">
-        <f>H86/1000</f>
+        <f>H87/1000</f>
         <v/>
       </c>
     </row>
@@ -13543,11 +13572,11 @@
         <v/>
       </c>
       <c r="G94" s="433">
-        <f>G87/1000</f>
+        <f>G88/1000</f>
         <v/>
       </c>
       <c r="H94" s="433">
-        <f>H87/1000</f>
+        <f>H88/1000</f>
         <v/>
       </c>
     </row>
@@ -13682,6 +13711,31 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.006944444444444444" bottom="0.006944444444444444" header="0.002777777777777778" footer="0.002777777777777778"/>
   <pageSetup orientation="portrait" paperSize="9" scale="82" fitToHeight="0"/>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -19727,6 +19781,31 @@
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.006944444444444444" bottom="0.006944444444444444" header="0.002777777777777778" footer="0.002777777777777778"/>
   <pageSetup orientation="landscape" paperSize="9" scale="32"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -21418,19 +21497,19 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>INPUT!D117</f>
+        <f>TEXT(INPUT!D117,"0")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>INPUT!D117-3</f>
+        <f>TEXT(INPUT!D117-3,"0")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>INPUT!D117-2</f>
+        <f>TEXT(INPUT!D117-2,"0")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>INPUT!D117-1</f>
+        <f>TEXT(INPUT!D117-1,"0")</f>
         <v/>
       </c>
       <c r="H5" s="16">
@@ -23295,6 +23374,31 @@
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.006944444444444444" bottom="0.006944444444444444" header="0.002777777777777778" footer="0.002777777777777778"/>
   <pageSetup orientation="landscape" paperSize="9" scale="97"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 

--- a/assets/TEMPLATE.xlsx
+++ b/assets/TEMPLATE.xlsx
@@ -3006,8 +3006,6 @@
         <axId val="1373965104"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="150000"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -4009,8 +4007,6 @@
         <axId val="1412916896"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="700000"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -4786,8 +4782,6 @@
         <axId val="766619103"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="800000"/>
-          <min val="300000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5208,8 +5202,6 @@
         <axId val="1411817344"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="300000"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -6254,8 +6246,6 @@
         <axId val="1578285791"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="130"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="b"/>
@@ -14988,6 +14978,31 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.006944444444444444" bottom="0.006944444444444444" header="0.002777777777777778" footer="0.002777777777777778"/>
   <pageSetup orientation="landscape" paperSize="9" scale="81"/>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -16189,6 +16204,31 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.006944444444444444" bottom="0.006944444444444444" header="0.002777777777777778" footer="0.002777777777777778"/>
   <pageSetup orientation="portrait" paperSize="9" scale="84" fitToHeight="0"/>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 

--- a/assets/TEMPLATE.xlsx
+++ b/assets/TEMPLATE.xlsx
@@ -25589,6 +25589,61 @@
     <brk id="41" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <conditionalFormatting sqref="C1:C200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H200">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J200">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K200">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L200">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M200">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N200">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -28168,5 +28223,30 @@
   <pageMargins left="0.005555555555555556" right="0.005555555555555556" top="0.005555555555555556" bottom="0.005555555555555556" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <conditionalFormatting sqref="T1:T200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>INPUT!$F$128&lt;5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U1:U200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>INPUT!$F$128&lt;4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V1:V200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>INPUT!$F$128&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W1:W200">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>INPUT!$F$128&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1:X200">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>INPUT!$F$128&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>